--- a/table/resources/sample/RobotAction_Bet.xlsx
+++ b/table/resources/sample/RobotAction_Bet.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\bet\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27DFED2-39CB-4FE8-AE94-0AC1A87B2586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BetRobot" sheetId="1" r:id="rId1"/>
@@ -27,18 +33,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -47,6 +54,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -55,13 +63,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -70,6 +79,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -79,13 +89,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -94,6 +105,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -103,13 +115,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -118,6 +131,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -127,13 +141,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -142,6 +157,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -150,13 +166,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -165,6 +182,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -178,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="73">
   <si>
     <t>序列</t>
   </si>
@@ -402,14 +420,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,170 +433,45 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,240 +480,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -834,268 +535,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1123,90 +582,159 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1217,7 +745,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1245,154 +773,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1642,14 +1056,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J304"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="12.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
@@ -1660,7 +1074,7 @@
     <col min="10" max="10" width="28.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1688,7 +1102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1716,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1744,13 +1158,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>100001</v>
       </c>
@@ -1782,7 +1196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>100002</v>
       </c>
@@ -1814,7 +1228,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>100003</v>
       </c>
@@ -1846,7 +1260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>100004</v>
       </c>
@@ -1878,7 +1292,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>100005</v>
       </c>
@@ -1910,7 +1324,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>100006</v>
       </c>
@@ -1942,7 +1356,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>100007</v>
       </c>
@@ -1974,7 +1388,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>100008</v>
       </c>
@@ -2006,7 +1420,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>100009</v>
       </c>
@@ -2038,7 +1452,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>100010</v>
       </c>
@@ -2070,7 +1484,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>100011</v>
       </c>
@@ -2102,7 +1516,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>100012</v>
       </c>
@@ -2134,7 +1548,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>100013</v>
       </c>
@@ -2166,7 +1580,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>100014</v>
       </c>
@@ -2198,7 +1612,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>100015</v>
       </c>
@@ -2230,7 +1644,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>100016</v>
       </c>
@@ -2262,7 +1676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>100017</v>
       </c>
@@ -2294,7 +1708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>100018</v>
       </c>
@@ -2326,7 +1740,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>100019</v>
       </c>
@@ -2358,7 +1772,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>100020</v>
       </c>
@@ -2390,7 +1804,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>100021</v>
       </c>
@@ -2422,7 +1836,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>100022</v>
       </c>
@@ -2454,7 +1868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>100023</v>
       </c>
@@ -2486,7 +1900,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>100024</v>
       </c>
@@ -2518,7 +1932,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>100025</v>
       </c>
@@ -2550,7 +1964,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>100026</v>
       </c>
@@ -2582,7 +1996,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>100027</v>
       </c>
@@ -2614,7 +2028,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>100028</v>
       </c>
@@ -2646,7 +2060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>100029</v>
       </c>
@@ -2678,7 +2092,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>100030</v>
       </c>
@@ -2710,7 +2124,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>100031</v>
       </c>
@@ -2742,7 +2156,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>100032</v>
       </c>
@@ -2774,7 +2188,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>100033</v>
       </c>
@@ -2806,7 +2220,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>100034</v>
       </c>
@@ -2838,7 +2252,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>100035</v>
       </c>
@@ -2870,7 +2284,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>100036</v>
       </c>
@@ -2902,7 +2316,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>100037</v>
       </c>
@@ -2934,7 +2348,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>100038</v>
       </c>
@@ -2966,7 +2380,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>100039</v>
       </c>
@@ -2998,7 +2412,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>100040</v>
       </c>
@@ -3030,7 +2444,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>100041</v>
       </c>
@@ -3062,7 +2476,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>100042</v>
       </c>
@@ -3094,7 +2508,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>100043</v>
       </c>
@@ -3126,7 +2540,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>100044</v>
       </c>
@@ -3158,7 +2572,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>100045</v>
       </c>
@@ -3190,7 +2604,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>100046</v>
       </c>
@@ -3222,7 +2636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>100047</v>
       </c>
@@ -3254,7 +2668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>100048</v>
       </c>
@@ -3286,7 +2700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>100049</v>
       </c>
@@ -3318,7 +2732,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>100050</v>
       </c>
@@ -3350,7 +2764,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>100051</v>
       </c>
@@ -3382,7 +2796,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>100052</v>
       </c>
@@ -3414,7 +2828,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>100053</v>
       </c>
@@ -3446,7 +2860,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>100054</v>
       </c>
@@ -3478,7 +2892,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>100055</v>
       </c>
@@ -3510,7 +2924,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>100056</v>
       </c>
@@ -3542,7 +2956,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>100057</v>
       </c>
@@ -3574,7 +2988,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>100058</v>
       </c>
@@ -3606,7 +3020,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>100059</v>
       </c>
@@ -3638,7 +3052,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>100060</v>
       </c>
@@ -3670,7 +3084,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>100061</v>
       </c>
@@ -3702,7 +3116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>100062</v>
       </c>
@@ -3734,7 +3148,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>100063</v>
       </c>
@@ -3766,7 +3180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>100064</v>
       </c>
@@ -3798,7 +3212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>100065</v>
       </c>
@@ -3830,7 +3244,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>100066</v>
       </c>
@@ -3862,7 +3276,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>100067</v>
       </c>
@@ -3894,7 +3308,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>100068</v>
       </c>
@@ -3926,7 +3340,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>100069</v>
       </c>
@@ -3958,7 +3372,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>100070</v>
       </c>
@@ -3990,7 +3404,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>100071</v>
       </c>
@@ -4022,7 +3436,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>100072</v>
       </c>
@@ -4054,7 +3468,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>100073</v>
       </c>
@@ -4086,7 +3500,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>100074</v>
       </c>
@@ -4118,7 +3532,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>100075</v>
       </c>
@@ -4150,7 +3564,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>100076</v>
       </c>
@@ -4182,7 +3596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>100077</v>
       </c>
@@ -4214,7 +3628,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>100078</v>
       </c>
@@ -4246,7 +3660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>100079</v>
       </c>
@@ -4278,7 +3692,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>100080</v>
       </c>
@@ -4310,7 +3724,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>100081</v>
       </c>
@@ -4342,7 +3756,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>100082</v>
       </c>
@@ -4374,7 +3788,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>100083</v>
       </c>
@@ -4406,7 +3820,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>100084</v>
       </c>
@@ -4438,7 +3852,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>100085</v>
       </c>
@@ -4470,7 +3884,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>100086</v>
       </c>
@@ -4502,7 +3916,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>100087</v>
       </c>
@@ -4534,7 +3948,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>100088</v>
       </c>
@@ -4566,7 +3980,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>100089</v>
       </c>
@@ -4598,7 +4012,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>100090</v>
       </c>
@@ -4630,7 +4044,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>100091</v>
       </c>
@@ -4662,7 +4076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>100092</v>
       </c>
@@ -4694,7 +4108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>100093</v>
       </c>
@@ -4726,7 +4140,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>100094</v>
       </c>
@@ -4758,7 +4172,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>100095</v>
       </c>
@@ -4790,7 +4204,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>100096</v>
       </c>
@@ -4822,7 +4236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>100097</v>
       </c>
@@ -4854,7 +4268,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>100098</v>
       </c>
@@ -4886,7 +4300,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>100099</v>
       </c>
@@ -4918,7 +4332,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A104">
         <v>100100</v>
       </c>
@@ -4950,7 +4364,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A105">
         <v>100101</v>
       </c>
@@ -4982,7 +4396,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A106">
         <v>100102</v>
       </c>
@@ -5014,7 +4428,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A107">
         <v>100103</v>
       </c>
@@ -5046,7 +4460,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A108">
         <v>100104</v>
       </c>
@@ -5078,7 +4492,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A109">
         <v>100105</v>
       </c>
@@ -5110,7 +4524,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A110">
         <v>100106</v>
       </c>
@@ -5142,7 +4556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A111">
         <v>100107</v>
       </c>
@@ -5174,7 +4588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A112">
         <v>100108</v>
       </c>
@@ -5206,7 +4620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A113">
         <v>100109</v>
       </c>
@@ -5238,7 +4652,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A114">
         <v>100110</v>
       </c>
@@ -5270,7 +4684,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A115">
         <v>100111</v>
       </c>
@@ -5302,7 +4716,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A116">
         <v>100112</v>
       </c>
@@ -5334,7 +4748,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A117">
         <v>100113</v>
       </c>
@@ -5366,7 +4780,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A118">
         <v>100114</v>
       </c>
@@ -5398,7 +4812,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A119">
         <v>100115</v>
       </c>
@@ -5430,7 +4844,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A120">
         <v>100116</v>
       </c>
@@ -5462,7 +4876,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A121">
         <v>100117</v>
       </c>
@@ -5494,7 +4908,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A122">
         <v>100118</v>
       </c>
@@ -5526,7 +4940,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A123">
         <v>100119</v>
       </c>
@@ -5558,7 +4972,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A124">
         <v>100120</v>
       </c>
@@ -5590,7 +5004,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A125">
         <v>100121</v>
       </c>
@@ -5622,7 +5036,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A126">
         <v>100122</v>
       </c>
@@ -5654,7 +5068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A127">
         <v>100123</v>
       </c>
@@ -5686,7 +5100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A128">
         <v>100124</v>
       </c>
@@ -5718,7 +5132,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A129">
         <v>100125</v>
       </c>
@@ -5750,7 +5164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A130">
         <v>100126</v>
       </c>
@@ -5782,7 +5196,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A131">
         <v>100127</v>
       </c>
@@ -5814,7 +5228,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A132">
         <v>100128</v>
       </c>
@@ -5846,7 +5260,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A133">
         <v>100129</v>
       </c>
@@ -5878,7 +5292,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A134">
         <v>100130</v>
       </c>
@@ -5910,7 +5324,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A135">
         <v>100131</v>
       </c>
@@ -5942,7 +5356,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A136">
         <v>100132</v>
       </c>
@@ -5974,7 +5388,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A137">
         <v>100133</v>
       </c>
@@ -6006,7 +5420,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A138">
         <v>100134</v>
       </c>
@@ -6038,7 +5452,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A139">
         <v>100135</v>
       </c>
@@ -6070,7 +5484,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A140">
         <v>100136</v>
       </c>
@@ -6102,7 +5516,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A141">
         <v>100137</v>
       </c>
@@ -6134,7 +5548,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A142">
         <v>100138</v>
       </c>
@@ -6166,7 +5580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A143">
         <v>100139</v>
       </c>
@@ -6198,7 +5612,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A144">
         <v>100140</v>
       </c>
@@ -6230,7 +5644,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A145">
         <v>100141</v>
       </c>
@@ -6262,7 +5676,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A146">
         <v>100142</v>
       </c>
@@ -6294,7 +5708,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A147">
         <v>100143</v>
       </c>
@@ -6326,7 +5740,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A148">
         <v>100144</v>
       </c>
@@ -6358,7 +5772,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A149">
         <v>100145</v>
       </c>
@@ -6390,7 +5804,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A150">
         <v>100146</v>
       </c>
@@ -6422,7 +5836,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A151">
         <v>100147</v>
       </c>
@@ -6454,7 +5868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A152">
         <v>100148</v>
       </c>
@@ -6486,7 +5900,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A153">
         <v>100149</v>
       </c>
@@ -6518,7 +5932,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A154">
         <v>100150</v>
       </c>
@@ -6550,9 +5964,4809 @@
         <v>32</v>
       </c>
     </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A155">
+        <v>100151</v>
+      </c>
+      <c r="B155" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D155" s="5">
+        <v>20040021</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F155">
+        <v>9000</v>
+      </c>
+      <c r="G155" t="s">
+        <v>21</v>
+      </c>
+      <c r="H155" t="s">
+        <v>22</v>
+      </c>
+      <c r="I155" t="s">
+        <v>23</v>
+      </c>
+      <c r="J155" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A156">
+        <v>100152</v>
+      </c>
+      <c r="B156" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156" s="5">
+        <v>20040022</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F156">
+        <v>9000</v>
+      </c>
+      <c r="G156" t="s">
+        <v>21</v>
+      </c>
+      <c r="H156" t="s">
+        <v>22</v>
+      </c>
+      <c r="I156" t="s">
+        <v>23</v>
+      </c>
+      <c r="J156" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A157">
+        <v>100153</v>
+      </c>
+      <c r="B157" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D157" s="5">
+        <v>20040023</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F157">
+        <v>9000</v>
+      </c>
+      <c r="G157" t="s">
+        <v>21</v>
+      </c>
+      <c r="H157" t="s">
+        <v>22</v>
+      </c>
+      <c r="I157" t="s">
+        <v>23</v>
+      </c>
+      <c r="J157" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A158">
+        <v>100154</v>
+      </c>
+      <c r="B158" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D158" s="5">
+        <v>20040021</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F158">
+        <v>7000</v>
+      </c>
+      <c r="G158" t="s">
+        <v>28</v>
+      </c>
+      <c r="H158" t="s">
+        <v>22</v>
+      </c>
+      <c r="I158" t="s">
+        <v>23</v>
+      </c>
+      <c r="J158" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A159">
+        <v>100155</v>
+      </c>
+      <c r="B159" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D159" s="5">
+        <v>20040022</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F159">
+        <v>7000</v>
+      </c>
+      <c r="G159" t="s">
+        <v>28</v>
+      </c>
+      <c r="H159" t="s">
+        <v>22</v>
+      </c>
+      <c r="I159" t="s">
+        <v>23</v>
+      </c>
+      <c r="J159" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A160">
+        <v>100156</v>
+      </c>
+      <c r="B160" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D160" s="5">
+        <v>20040023</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F160">
+        <v>7000</v>
+      </c>
+      <c r="G160" t="s">
+        <v>28</v>
+      </c>
+      <c r="H160" t="s">
+        <v>22</v>
+      </c>
+      <c r="I160" t="s">
+        <v>23</v>
+      </c>
+      <c r="J160" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A161">
+        <v>100157</v>
+      </c>
+      <c r="B161" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D161" s="5">
+        <v>20040021</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F161">
+        <v>5000</v>
+      </c>
+      <c r="G161" t="s">
+        <v>31</v>
+      </c>
+      <c r="H161" t="s">
+        <v>22</v>
+      </c>
+      <c r="I161" t="s">
+        <v>23</v>
+      </c>
+      <c r="J161" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A162">
+        <v>100158</v>
+      </c>
+      <c r="B162" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D162" s="5">
+        <v>20040022</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F162">
+        <v>5000</v>
+      </c>
+      <c r="G162" t="s">
+        <v>31</v>
+      </c>
+      <c r="H162" t="s">
+        <v>22</v>
+      </c>
+      <c r="I162" t="s">
+        <v>23</v>
+      </c>
+      <c r="J162" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A163">
+        <v>100159</v>
+      </c>
+      <c r="B163" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D163" s="5">
+        <v>20040023</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F163">
+        <v>5000</v>
+      </c>
+      <c r="G163" t="s">
+        <v>31</v>
+      </c>
+      <c r="H163" t="s">
+        <v>22</v>
+      </c>
+      <c r="I163" t="s">
+        <v>23</v>
+      </c>
+      <c r="J163" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A164">
+        <v>100160</v>
+      </c>
+      <c r="B164" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D164" s="5">
+        <v>20040021</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F164">
+        <v>4000</v>
+      </c>
+      <c r="G164" t="s">
+        <v>34</v>
+      </c>
+      <c r="H164" t="s">
+        <v>22</v>
+      </c>
+      <c r="I164" t="s">
+        <v>23</v>
+      </c>
+      <c r="J164" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A165">
+        <v>100161</v>
+      </c>
+      <c r="B165" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D165" s="5">
+        <v>20040022</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F165">
+        <v>4000</v>
+      </c>
+      <c r="G165" t="s">
+        <v>34</v>
+      </c>
+      <c r="H165" t="s">
+        <v>22</v>
+      </c>
+      <c r="I165" t="s">
+        <v>23</v>
+      </c>
+      <c r="J165" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A166">
+        <v>100162</v>
+      </c>
+      <c r="B166" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D166" s="5">
+        <v>20040023</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F166">
+        <v>4000</v>
+      </c>
+      <c r="G166" t="s">
+        <v>34</v>
+      </c>
+      <c r="H166" t="s">
+        <v>22</v>
+      </c>
+      <c r="I166" t="s">
+        <v>23</v>
+      </c>
+      <c r="J166" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A167">
+        <v>100163</v>
+      </c>
+      <c r="B167" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D167" s="5">
+        <v>20040021</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F167">
+        <v>2000</v>
+      </c>
+      <c r="G167" t="s">
+        <v>36</v>
+      </c>
+      <c r="H167" t="s">
+        <v>22</v>
+      </c>
+      <c r="I167" t="s">
+        <v>23</v>
+      </c>
+      <c r="J167" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A168">
+        <v>100164</v>
+      </c>
+      <c r="B168" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D168" s="5">
+        <v>20040022</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F168">
+        <v>2000</v>
+      </c>
+      <c r="G168" t="s">
+        <v>36</v>
+      </c>
+      <c r="H168" t="s">
+        <v>22</v>
+      </c>
+      <c r="I168" t="s">
+        <v>23</v>
+      </c>
+      <c r="J168" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A169">
+        <v>100165</v>
+      </c>
+      <c r="B169" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D169" s="5">
+        <v>20040023</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F169">
+        <v>2000</v>
+      </c>
+      <c r="G169" t="s">
+        <v>36</v>
+      </c>
+      <c r="H169" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" t="s">
+        <v>23</v>
+      </c>
+      <c r="J169" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A170">
+        <v>100166</v>
+      </c>
+      <c r="B170" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D170" s="5">
+        <v>20050021</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F170">
+        <v>9000</v>
+      </c>
+      <c r="G170" t="s">
+        <v>21</v>
+      </c>
+      <c r="H170" t="s">
+        <v>38</v>
+      </c>
+      <c r="I170" t="s">
+        <v>23</v>
+      </c>
+      <c r="J170" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A171">
+        <v>100167</v>
+      </c>
+      <c r="B171" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D171" s="5">
+        <v>20050022</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F171">
+        <v>9000</v>
+      </c>
+      <c r="G171" t="s">
+        <v>21</v>
+      </c>
+      <c r="H171" t="s">
+        <v>38</v>
+      </c>
+      <c r="I171" t="s">
+        <v>23</v>
+      </c>
+      <c r="J171" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A172">
+        <v>100168</v>
+      </c>
+      <c r="B172" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D172" s="5">
+        <v>20050023</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F172">
+        <v>9000</v>
+      </c>
+      <c r="G172" t="s">
+        <v>21</v>
+      </c>
+      <c r="H172" t="s">
+        <v>38</v>
+      </c>
+      <c r="I172" t="s">
+        <v>23</v>
+      </c>
+      <c r="J172" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A173">
+        <v>100169</v>
+      </c>
+      <c r="B173" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D173" s="5">
+        <v>20050021</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F173">
+        <v>7000</v>
+      </c>
+      <c r="G173" t="s">
+        <v>28</v>
+      </c>
+      <c r="H173" t="s">
+        <v>38</v>
+      </c>
+      <c r="I173" t="s">
+        <v>23</v>
+      </c>
+      <c r="J173" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A174">
+        <v>100170</v>
+      </c>
+      <c r="B174" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D174" s="5">
+        <v>20050022</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F174">
+        <v>7000</v>
+      </c>
+      <c r="G174" t="s">
+        <v>28</v>
+      </c>
+      <c r="H174" t="s">
+        <v>38</v>
+      </c>
+      <c r="I174" t="s">
+        <v>23</v>
+      </c>
+      <c r="J174" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A175">
+        <v>100171</v>
+      </c>
+      <c r="B175" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D175" s="5">
+        <v>20050023</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F175">
+        <v>7000</v>
+      </c>
+      <c r="G175" t="s">
+        <v>28</v>
+      </c>
+      <c r="H175" t="s">
+        <v>38</v>
+      </c>
+      <c r="I175" t="s">
+        <v>23</v>
+      </c>
+      <c r="J175" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A176">
+        <v>100172</v>
+      </c>
+      <c r="B176" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D176" s="5">
+        <v>20050021</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F176">
+        <v>5000</v>
+      </c>
+      <c r="G176" t="s">
+        <v>31</v>
+      </c>
+      <c r="H176" t="s">
+        <v>38</v>
+      </c>
+      <c r="I176" t="s">
+        <v>23</v>
+      </c>
+      <c r="J176" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A177">
+        <v>100173</v>
+      </c>
+      <c r="B177" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D177" s="5">
+        <v>20050022</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F177">
+        <v>5000</v>
+      </c>
+      <c r="G177" t="s">
+        <v>31</v>
+      </c>
+      <c r="H177" t="s">
+        <v>38</v>
+      </c>
+      <c r="I177" t="s">
+        <v>23</v>
+      </c>
+      <c r="J177" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A178">
+        <v>100174</v>
+      </c>
+      <c r="B178" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D178" s="5">
+        <v>20050023</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F178">
+        <v>5000</v>
+      </c>
+      <c r="G178" t="s">
+        <v>31</v>
+      </c>
+      <c r="H178" t="s">
+        <v>38</v>
+      </c>
+      <c r="I178" t="s">
+        <v>23</v>
+      </c>
+      <c r="J178" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A179">
+        <v>100175</v>
+      </c>
+      <c r="B179" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D179" s="5">
+        <v>20050021</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F179">
+        <v>4000</v>
+      </c>
+      <c r="G179" t="s">
+        <v>34</v>
+      </c>
+      <c r="H179" t="s">
+        <v>38</v>
+      </c>
+      <c r="I179" t="s">
+        <v>23</v>
+      </c>
+      <c r="J179" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A180">
+        <v>100176</v>
+      </c>
+      <c r="B180" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D180" s="5">
+        <v>20050022</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F180">
+        <v>4000</v>
+      </c>
+      <c r="G180" t="s">
+        <v>34</v>
+      </c>
+      <c r="H180" t="s">
+        <v>38</v>
+      </c>
+      <c r="I180" t="s">
+        <v>23</v>
+      </c>
+      <c r="J180" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A181">
+        <v>100177</v>
+      </c>
+      <c r="B181" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D181" s="5">
+        <v>20050023</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F181">
+        <v>4000</v>
+      </c>
+      <c r="G181" t="s">
+        <v>34</v>
+      </c>
+      <c r="H181" t="s">
+        <v>38</v>
+      </c>
+      <c r="I181" t="s">
+        <v>23</v>
+      </c>
+      <c r="J181" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A182">
+        <v>100178</v>
+      </c>
+      <c r="B182" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D182" s="5">
+        <v>20050021</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F182">
+        <v>2000</v>
+      </c>
+      <c r="G182" t="s">
+        <v>36</v>
+      </c>
+      <c r="H182" t="s">
+        <v>38</v>
+      </c>
+      <c r="I182" t="s">
+        <v>23</v>
+      </c>
+      <c r="J182" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A183">
+        <v>100179</v>
+      </c>
+      <c r="B183" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D183" s="5">
+        <v>20050022</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F183">
+        <v>2000</v>
+      </c>
+      <c r="G183" t="s">
+        <v>36</v>
+      </c>
+      <c r="H183" t="s">
+        <v>38</v>
+      </c>
+      <c r="I183" t="s">
+        <v>23</v>
+      </c>
+      <c r="J183" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A184">
+        <v>100180</v>
+      </c>
+      <c r="B184" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D184" s="5">
+        <v>20050023</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F184">
+        <v>2000</v>
+      </c>
+      <c r="G184" t="s">
+        <v>36</v>
+      </c>
+      <c r="H184" t="s">
+        <v>38</v>
+      </c>
+      <c r="I184" t="s">
+        <v>23</v>
+      </c>
+      <c r="J184" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A185">
+        <v>100181</v>
+      </c>
+      <c r="B185" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D185" s="5">
+        <v>20010021</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F185">
+        <v>9000</v>
+      </c>
+      <c r="G185" t="s">
+        <v>21</v>
+      </c>
+      <c r="H185" t="s">
+        <v>42</v>
+      </c>
+      <c r="I185" t="s">
+        <v>23</v>
+      </c>
+      <c r="J185" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A186">
+        <v>100182</v>
+      </c>
+      <c r="B186" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D186" s="5">
+        <v>20010022</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F186">
+        <v>9000</v>
+      </c>
+      <c r="G186" t="s">
+        <v>21</v>
+      </c>
+      <c r="H186" t="s">
+        <v>42</v>
+      </c>
+      <c r="I186" t="s">
+        <v>23</v>
+      </c>
+      <c r="J186" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A187">
+        <v>100183</v>
+      </c>
+      <c r="B187" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D187" s="5">
+        <v>20010023</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F187">
+        <v>9000</v>
+      </c>
+      <c r="G187" t="s">
+        <v>21</v>
+      </c>
+      <c r="H187" t="s">
+        <v>42</v>
+      </c>
+      <c r="I187" t="s">
+        <v>23</v>
+      </c>
+      <c r="J187" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A188">
+        <v>100184</v>
+      </c>
+      <c r="B188" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D188" s="5">
+        <v>20010021</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F188">
+        <v>7000</v>
+      </c>
+      <c r="G188" t="s">
+        <v>28</v>
+      </c>
+      <c r="H188" t="s">
+        <v>42</v>
+      </c>
+      <c r="I188" t="s">
+        <v>23</v>
+      </c>
+      <c r="J188" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A189">
+        <v>100185</v>
+      </c>
+      <c r="B189" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D189" s="5">
+        <v>20010022</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F189">
+        <v>7000</v>
+      </c>
+      <c r="G189" t="s">
+        <v>28</v>
+      </c>
+      <c r="H189" t="s">
+        <v>42</v>
+      </c>
+      <c r="I189" t="s">
+        <v>23</v>
+      </c>
+      <c r="J189" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A190">
+        <v>100186</v>
+      </c>
+      <c r="B190" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D190" s="5">
+        <v>20010023</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F190">
+        <v>7000</v>
+      </c>
+      <c r="G190" t="s">
+        <v>28</v>
+      </c>
+      <c r="H190" t="s">
+        <v>42</v>
+      </c>
+      <c r="I190" t="s">
+        <v>23</v>
+      </c>
+      <c r="J190" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A191">
+        <v>100187</v>
+      </c>
+      <c r="B191" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D191" s="5">
+        <v>20010021</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F191">
+        <v>5000</v>
+      </c>
+      <c r="G191" t="s">
+        <v>31</v>
+      </c>
+      <c r="H191" t="s">
+        <v>42</v>
+      </c>
+      <c r="I191" t="s">
+        <v>23</v>
+      </c>
+      <c r="J191" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A192">
+        <v>100188</v>
+      </c>
+      <c r="B192" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D192" s="5">
+        <v>20010022</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F192">
+        <v>5000</v>
+      </c>
+      <c r="G192" t="s">
+        <v>31</v>
+      </c>
+      <c r="H192" t="s">
+        <v>42</v>
+      </c>
+      <c r="I192" t="s">
+        <v>23</v>
+      </c>
+      <c r="J192" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A193">
+        <v>100189</v>
+      </c>
+      <c r="B193" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D193" s="5">
+        <v>20010023</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F193">
+        <v>5000</v>
+      </c>
+      <c r="G193" t="s">
+        <v>31</v>
+      </c>
+      <c r="H193" t="s">
+        <v>42</v>
+      </c>
+      <c r="I193" t="s">
+        <v>23</v>
+      </c>
+      <c r="J193" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A194">
+        <v>100190</v>
+      </c>
+      <c r="B194" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D194" s="5">
+        <v>20010021</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F194">
+        <v>4000</v>
+      </c>
+      <c r="G194" t="s">
+        <v>34</v>
+      </c>
+      <c r="H194" t="s">
+        <v>42</v>
+      </c>
+      <c r="I194" t="s">
+        <v>23</v>
+      </c>
+      <c r="J194" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A195">
+        <v>100191</v>
+      </c>
+      <c r="B195" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D195" s="5">
+        <v>20010022</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F195">
+        <v>4000</v>
+      </c>
+      <c r="G195" t="s">
+        <v>34</v>
+      </c>
+      <c r="H195" t="s">
+        <v>42</v>
+      </c>
+      <c r="I195" t="s">
+        <v>23</v>
+      </c>
+      <c r="J195" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A196">
+        <v>100192</v>
+      </c>
+      <c r="B196" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D196" s="5">
+        <v>20010023</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F196">
+        <v>4000</v>
+      </c>
+      <c r="G196" t="s">
+        <v>34</v>
+      </c>
+      <c r="H196" t="s">
+        <v>42</v>
+      </c>
+      <c r="I196" t="s">
+        <v>23</v>
+      </c>
+      <c r="J196" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A197">
+        <v>100193</v>
+      </c>
+      <c r="B197" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D197" s="5">
+        <v>20010021</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F197">
+        <v>2000</v>
+      </c>
+      <c r="G197" t="s">
+        <v>36</v>
+      </c>
+      <c r="H197" t="s">
+        <v>42</v>
+      </c>
+      <c r="I197" t="s">
+        <v>23</v>
+      </c>
+      <c r="J197" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A198">
+        <v>100194</v>
+      </c>
+      <c r="B198" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D198" s="5">
+        <v>20010022</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F198">
+        <v>2000</v>
+      </c>
+      <c r="G198" t="s">
+        <v>36</v>
+      </c>
+      <c r="H198" t="s">
+        <v>42</v>
+      </c>
+      <c r="I198" t="s">
+        <v>23</v>
+      </c>
+      <c r="J198" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A199">
+        <v>100195</v>
+      </c>
+      <c r="B199" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D199" s="5">
+        <v>20010023</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F199">
+        <v>2000</v>
+      </c>
+      <c r="G199" t="s">
+        <v>36</v>
+      </c>
+      <c r="H199" t="s">
+        <v>42</v>
+      </c>
+      <c r="I199" t="s">
+        <v>23</v>
+      </c>
+      <c r="J199" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A200">
+        <v>100196</v>
+      </c>
+      <c r="B200" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D200" s="5">
+        <v>20030021</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F200">
+        <v>9000</v>
+      </c>
+      <c r="G200" t="s">
+        <v>21</v>
+      </c>
+      <c r="H200" t="s">
+        <v>46</v>
+      </c>
+      <c r="I200" t="s">
+        <v>23</v>
+      </c>
+      <c r="J200" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A201">
+        <v>100197</v>
+      </c>
+      <c r="B201" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D201" s="5">
+        <v>20030022</v>
+      </c>
+      <c r="E201" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F201">
+        <v>9000</v>
+      </c>
+      <c r="G201" t="s">
+        <v>21</v>
+      </c>
+      <c r="H201" t="s">
+        <v>46</v>
+      </c>
+      <c r="I201" t="s">
+        <v>23</v>
+      </c>
+      <c r="J201" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A202">
+        <v>100198</v>
+      </c>
+      <c r="B202" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D202" s="5">
+        <v>20030023</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F202">
+        <v>9000</v>
+      </c>
+      <c r="G202" t="s">
+        <v>21</v>
+      </c>
+      <c r="H202" t="s">
+        <v>46</v>
+      </c>
+      <c r="I202" t="s">
+        <v>23</v>
+      </c>
+      <c r="J202" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A203">
+        <v>100199</v>
+      </c>
+      <c r="B203" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D203" s="5">
+        <v>20030021</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F203">
+        <v>7000</v>
+      </c>
+      <c r="G203" t="s">
+        <v>28</v>
+      </c>
+      <c r="H203" t="s">
+        <v>46</v>
+      </c>
+      <c r="I203" t="s">
+        <v>23</v>
+      </c>
+      <c r="J203" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A204">
+        <v>100200</v>
+      </c>
+      <c r="B204" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204" s="5">
+        <v>20030022</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F204">
+        <v>7000</v>
+      </c>
+      <c r="G204" t="s">
+        <v>28</v>
+      </c>
+      <c r="H204" t="s">
+        <v>46</v>
+      </c>
+      <c r="I204" t="s">
+        <v>23</v>
+      </c>
+      <c r="J204" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A205">
+        <v>100201</v>
+      </c>
+      <c r="B205" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D205" s="5">
+        <v>20030023</v>
+      </c>
+      <c r="E205" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F205">
+        <v>7000</v>
+      </c>
+      <c r="G205" t="s">
+        <v>28</v>
+      </c>
+      <c r="H205" t="s">
+        <v>46</v>
+      </c>
+      <c r="I205" t="s">
+        <v>23</v>
+      </c>
+      <c r="J205" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A206">
+        <v>100202</v>
+      </c>
+      <c r="B206" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D206" s="5">
+        <v>20030021</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F206">
+        <v>5000</v>
+      </c>
+      <c r="G206" t="s">
+        <v>31</v>
+      </c>
+      <c r="H206" t="s">
+        <v>46</v>
+      </c>
+      <c r="I206" t="s">
+        <v>23</v>
+      </c>
+      <c r="J206" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A207">
+        <v>100203</v>
+      </c>
+      <c r="B207" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D207" s="5">
+        <v>20030022</v>
+      </c>
+      <c r="E207" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F207">
+        <v>5000</v>
+      </c>
+      <c r="G207" t="s">
+        <v>31</v>
+      </c>
+      <c r="H207" t="s">
+        <v>46</v>
+      </c>
+      <c r="I207" t="s">
+        <v>23</v>
+      </c>
+      <c r="J207" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A208">
+        <v>100204</v>
+      </c>
+      <c r="B208" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D208" s="5">
+        <v>20030023</v>
+      </c>
+      <c r="E208" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F208">
+        <v>5000</v>
+      </c>
+      <c r="G208" t="s">
+        <v>31</v>
+      </c>
+      <c r="H208" t="s">
+        <v>46</v>
+      </c>
+      <c r="I208" t="s">
+        <v>23</v>
+      </c>
+      <c r="J208" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A209">
+        <v>100205</v>
+      </c>
+      <c r="B209" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D209" s="5">
+        <v>20030021</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F209">
+        <v>4000</v>
+      </c>
+      <c r="G209" t="s">
+        <v>34</v>
+      </c>
+      <c r="H209" t="s">
+        <v>46</v>
+      </c>
+      <c r="I209" t="s">
+        <v>23</v>
+      </c>
+      <c r="J209" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A210">
+        <v>100206</v>
+      </c>
+      <c r="B210" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D210" s="5">
+        <v>20030022</v>
+      </c>
+      <c r="E210" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F210">
+        <v>4000</v>
+      </c>
+      <c r="G210" t="s">
+        <v>34</v>
+      </c>
+      <c r="H210" t="s">
+        <v>46</v>
+      </c>
+      <c r="I210" t="s">
+        <v>23</v>
+      </c>
+      <c r="J210" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A211">
+        <v>100207</v>
+      </c>
+      <c r="B211" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D211" s="5">
+        <v>20030023</v>
+      </c>
+      <c r="E211" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F211">
+        <v>4000</v>
+      </c>
+      <c r="G211" t="s">
+        <v>34</v>
+      </c>
+      <c r="H211" t="s">
+        <v>46</v>
+      </c>
+      <c r="I211" t="s">
+        <v>23</v>
+      </c>
+      <c r="J211" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A212">
+        <v>100208</v>
+      </c>
+      <c r="B212" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D212" s="5">
+        <v>20030021</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F212">
+        <v>2000</v>
+      </c>
+      <c r="G212" t="s">
+        <v>36</v>
+      </c>
+      <c r="H212" t="s">
+        <v>46</v>
+      </c>
+      <c r="I212" t="s">
+        <v>23</v>
+      </c>
+      <c r="J212" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A213">
+        <v>100209</v>
+      </c>
+      <c r="B213" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D213" s="5">
+        <v>20030022</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F213">
+        <v>2000</v>
+      </c>
+      <c r="G213" t="s">
+        <v>36</v>
+      </c>
+      <c r="H213" t="s">
+        <v>46</v>
+      </c>
+      <c r="I213" t="s">
+        <v>23</v>
+      </c>
+      <c r="J213" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A214">
+        <v>100210</v>
+      </c>
+      <c r="B214" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D214" s="5">
+        <v>20030023</v>
+      </c>
+      <c r="E214" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F214">
+        <v>2000</v>
+      </c>
+      <c r="G214" t="s">
+        <v>36</v>
+      </c>
+      <c r="H214" t="s">
+        <v>46</v>
+      </c>
+      <c r="I214" t="s">
+        <v>23</v>
+      </c>
+      <c r="J214" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A215">
+        <v>100211</v>
+      </c>
+      <c r="B215" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D215" s="5">
+        <v>20010121</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F215">
+        <v>9000</v>
+      </c>
+      <c r="G215" t="s">
+        <v>21</v>
+      </c>
+      <c r="H215" t="s">
+        <v>50</v>
+      </c>
+      <c r="I215" t="s">
+        <v>23</v>
+      </c>
+      <c r="J215" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A216">
+        <v>100212</v>
+      </c>
+      <c r="B216" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D216" s="5">
+        <v>20010122</v>
+      </c>
+      <c r="E216" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F216">
+        <v>9000</v>
+      </c>
+      <c r="G216" t="s">
+        <v>21</v>
+      </c>
+      <c r="H216" t="s">
+        <v>50</v>
+      </c>
+      <c r="I216" t="s">
+        <v>23</v>
+      </c>
+      <c r="J216" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A217">
+        <v>100213</v>
+      </c>
+      <c r="B217" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D217" s="5">
+        <v>20010123</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F217">
+        <v>9000</v>
+      </c>
+      <c r="G217" t="s">
+        <v>21</v>
+      </c>
+      <c r="H217" t="s">
+        <v>50</v>
+      </c>
+      <c r="I217" t="s">
+        <v>23</v>
+      </c>
+      <c r="J217" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A218">
+        <v>100214</v>
+      </c>
+      <c r="B218" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D218" s="5">
+        <v>20010121</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F218">
+        <v>7000</v>
+      </c>
+      <c r="G218" t="s">
+        <v>28</v>
+      </c>
+      <c r="H218" t="s">
+        <v>50</v>
+      </c>
+      <c r="I218" t="s">
+        <v>23</v>
+      </c>
+      <c r="J218" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A219">
+        <v>100215</v>
+      </c>
+      <c r="B219" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D219" s="5">
+        <v>20010122</v>
+      </c>
+      <c r="E219" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F219">
+        <v>7000</v>
+      </c>
+      <c r="G219" t="s">
+        <v>28</v>
+      </c>
+      <c r="H219" t="s">
+        <v>50</v>
+      </c>
+      <c r="I219" t="s">
+        <v>23</v>
+      </c>
+      <c r="J219" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A220">
+        <v>100216</v>
+      </c>
+      <c r="B220" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D220" s="5">
+        <v>20010123</v>
+      </c>
+      <c r="E220" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F220">
+        <v>7000</v>
+      </c>
+      <c r="G220" t="s">
+        <v>28</v>
+      </c>
+      <c r="H220" t="s">
+        <v>50</v>
+      </c>
+      <c r="I220" t="s">
+        <v>23</v>
+      </c>
+      <c r="J220" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A221">
+        <v>100217</v>
+      </c>
+      <c r="B221" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D221" s="5">
+        <v>20010121</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F221">
+        <v>5000</v>
+      </c>
+      <c r="G221" t="s">
+        <v>31</v>
+      </c>
+      <c r="H221" t="s">
+        <v>50</v>
+      </c>
+      <c r="I221" t="s">
+        <v>23</v>
+      </c>
+      <c r="J221" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A222">
+        <v>100218</v>
+      </c>
+      <c r="B222" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D222" s="5">
+        <v>20010122</v>
+      </c>
+      <c r="E222" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F222">
+        <v>5000</v>
+      </c>
+      <c r="G222" t="s">
+        <v>31</v>
+      </c>
+      <c r="H222" t="s">
+        <v>50</v>
+      </c>
+      <c r="I222" t="s">
+        <v>23</v>
+      </c>
+      <c r="J222" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A223">
+        <v>100219</v>
+      </c>
+      <c r="B223" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D223" s="5">
+        <v>20010123</v>
+      </c>
+      <c r="E223" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F223">
+        <v>5000</v>
+      </c>
+      <c r="G223" t="s">
+        <v>31</v>
+      </c>
+      <c r="H223" t="s">
+        <v>50</v>
+      </c>
+      <c r="I223" t="s">
+        <v>23</v>
+      </c>
+      <c r="J223" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A224">
+        <v>100220</v>
+      </c>
+      <c r="B224" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D224" s="5">
+        <v>20010121</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F224">
+        <v>4000</v>
+      </c>
+      <c r="G224" t="s">
+        <v>34</v>
+      </c>
+      <c r="H224" t="s">
+        <v>50</v>
+      </c>
+      <c r="I224" t="s">
+        <v>23</v>
+      </c>
+      <c r="J224" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A225">
+        <v>100221</v>
+      </c>
+      <c r="B225" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D225" s="5">
+        <v>20010122</v>
+      </c>
+      <c r="E225" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F225">
+        <v>4000</v>
+      </c>
+      <c r="G225" t="s">
+        <v>34</v>
+      </c>
+      <c r="H225" t="s">
+        <v>50</v>
+      </c>
+      <c r="I225" t="s">
+        <v>23</v>
+      </c>
+      <c r="J225" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A226">
+        <v>100222</v>
+      </c>
+      <c r="B226" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D226" s="5">
+        <v>20010123</v>
+      </c>
+      <c r="E226" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F226">
+        <v>4000</v>
+      </c>
+      <c r="G226" t="s">
+        <v>34</v>
+      </c>
+      <c r="H226" t="s">
+        <v>50</v>
+      </c>
+      <c r="I226" t="s">
+        <v>23</v>
+      </c>
+      <c r="J226" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A227">
+        <v>100223</v>
+      </c>
+      <c r="B227" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D227" s="5">
+        <v>20010121</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F227">
+        <v>2000</v>
+      </c>
+      <c r="G227" t="s">
+        <v>36</v>
+      </c>
+      <c r="H227" t="s">
+        <v>50</v>
+      </c>
+      <c r="I227" t="s">
+        <v>23</v>
+      </c>
+      <c r="J227" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A228">
+        <v>100224</v>
+      </c>
+      <c r="B228" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D228" s="5">
+        <v>20010122</v>
+      </c>
+      <c r="E228" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F228">
+        <v>2000</v>
+      </c>
+      <c r="G228" t="s">
+        <v>36</v>
+      </c>
+      <c r="H228" t="s">
+        <v>50</v>
+      </c>
+      <c r="I228" t="s">
+        <v>23</v>
+      </c>
+      <c r="J228" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A229">
+        <v>100225</v>
+      </c>
+      <c r="B229" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D229" s="5">
+        <v>20010123</v>
+      </c>
+      <c r="E229" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F229">
+        <v>2000</v>
+      </c>
+      <c r="G229" t="s">
+        <v>36</v>
+      </c>
+      <c r="H229" t="s">
+        <v>50</v>
+      </c>
+      <c r="I229" t="s">
+        <v>23</v>
+      </c>
+      <c r="J229" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A230">
+        <v>100226</v>
+      </c>
+      <c r="B230" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D230" s="5">
+        <v>20060021</v>
+      </c>
+      <c r="E230" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F230">
+        <v>9000</v>
+      </c>
+      <c r="G230" t="s">
+        <v>21</v>
+      </c>
+      <c r="H230" t="s">
+        <v>54</v>
+      </c>
+      <c r="I230" t="s">
+        <v>23</v>
+      </c>
+      <c r="J230" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A231">
+        <v>100227</v>
+      </c>
+      <c r="B231" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D231" s="5">
+        <v>20060022</v>
+      </c>
+      <c r="E231" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F231">
+        <v>9000</v>
+      </c>
+      <c r="G231" t="s">
+        <v>21</v>
+      </c>
+      <c r="H231" t="s">
+        <v>54</v>
+      </c>
+      <c r="I231" t="s">
+        <v>23</v>
+      </c>
+      <c r="J231" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A232">
+        <v>100228</v>
+      </c>
+      <c r="B232" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D232" s="5">
+        <v>20060023</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F232">
+        <v>9000</v>
+      </c>
+      <c r="G232" t="s">
+        <v>21</v>
+      </c>
+      <c r="H232" t="s">
+        <v>54</v>
+      </c>
+      <c r="I232" t="s">
+        <v>23</v>
+      </c>
+      <c r="J232" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A233">
+        <v>100229</v>
+      </c>
+      <c r="B233" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D233" s="5">
+        <v>20060021</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F233">
+        <v>7000</v>
+      </c>
+      <c r="G233" t="s">
+        <v>28</v>
+      </c>
+      <c r="H233" t="s">
+        <v>54</v>
+      </c>
+      <c r="I233" t="s">
+        <v>23</v>
+      </c>
+      <c r="J233" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A234">
+        <v>100230</v>
+      </c>
+      <c r="B234" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D234" s="5">
+        <v>20060022</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F234">
+        <v>7000</v>
+      </c>
+      <c r="G234" t="s">
+        <v>28</v>
+      </c>
+      <c r="H234" t="s">
+        <v>54</v>
+      </c>
+      <c r="I234" t="s">
+        <v>23</v>
+      </c>
+      <c r="J234" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A235">
+        <v>100231</v>
+      </c>
+      <c r="B235" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D235" s="5">
+        <v>20060023</v>
+      </c>
+      <c r="E235" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F235">
+        <v>7000</v>
+      </c>
+      <c r="G235" t="s">
+        <v>28</v>
+      </c>
+      <c r="H235" t="s">
+        <v>54</v>
+      </c>
+      <c r="I235" t="s">
+        <v>23</v>
+      </c>
+      <c r="J235" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A236">
+        <v>100232</v>
+      </c>
+      <c r="B236" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D236" s="5">
+        <v>20060021</v>
+      </c>
+      <c r="E236" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F236">
+        <v>5000</v>
+      </c>
+      <c r="G236" t="s">
+        <v>31</v>
+      </c>
+      <c r="H236" t="s">
+        <v>54</v>
+      </c>
+      <c r="I236" t="s">
+        <v>23</v>
+      </c>
+      <c r="J236" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A237">
+        <v>100233</v>
+      </c>
+      <c r="B237" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D237" s="5">
+        <v>20060022</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F237">
+        <v>5000</v>
+      </c>
+      <c r="G237" t="s">
+        <v>31</v>
+      </c>
+      <c r="H237" t="s">
+        <v>54</v>
+      </c>
+      <c r="I237" t="s">
+        <v>23</v>
+      </c>
+      <c r="J237" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A238">
+        <v>100234</v>
+      </c>
+      <c r="B238" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D238" s="5">
+        <v>20060023</v>
+      </c>
+      <c r="E238" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F238">
+        <v>5000</v>
+      </c>
+      <c r="G238" t="s">
+        <v>31</v>
+      </c>
+      <c r="H238" t="s">
+        <v>54</v>
+      </c>
+      <c r="I238" t="s">
+        <v>23</v>
+      </c>
+      <c r="J238" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A239">
+        <v>100235</v>
+      </c>
+      <c r="B239" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D239" s="5">
+        <v>20060021</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F239">
+        <v>4000</v>
+      </c>
+      <c r="G239" t="s">
+        <v>34</v>
+      </c>
+      <c r="H239" t="s">
+        <v>54</v>
+      </c>
+      <c r="I239" t="s">
+        <v>23</v>
+      </c>
+      <c r="J239" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A240">
+        <v>100236</v>
+      </c>
+      <c r="B240" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D240" s="5">
+        <v>20060022</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F240">
+        <v>4000</v>
+      </c>
+      <c r="G240" t="s">
+        <v>34</v>
+      </c>
+      <c r="H240" t="s">
+        <v>54</v>
+      </c>
+      <c r="I240" t="s">
+        <v>23</v>
+      </c>
+      <c r="J240" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A241">
+        <v>100237</v>
+      </c>
+      <c r="B241" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D241" s="5">
+        <v>20060023</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F241">
+        <v>4000</v>
+      </c>
+      <c r="G241" t="s">
+        <v>34</v>
+      </c>
+      <c r="H241" t="s">
+        <v>54</v>
+      </c>
+      <c r="I241" t="s">
+        <v>23</v>
+      </c>
+      <c r="J241" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A242">
+        <v>100238</v>
+      </c>
+      <c r="B242" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D242" s="5">
+        <v>20060021</v>
+      </c>
+      <c r="E242" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F242">
+        <v>2000</v>
+      </c>
+      <c r="G242" t="s">
+        <v>36</v>
+      </c>
+      <c r="H242" t="s">
+        <v>54</v>
+      </c>
+      <c r="I242" t="s">
+        <v>23</v>
+      </c>
+      <c r="J242" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A243">
+        <v>100239</v>
+      </c>
+      <c r="B243" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D243" s="5">
+        <v>20060022</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F243">
+        <v>2000</v>
+      </c>
+      <c r="G243" t="s">
+        <v>36</v>
+      </c>
+      <c r="H243" t="s">
+        <v>54</v>
+      </c>
+      <c r="I243" t="s">
+        <v>23</v>
+      </c>
+      <c r="J243" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A244">
+        <v>100240</v>
+      </c>
+      <c r="B244" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D244" s="5">
+        <v>20060023</v>
+      </c>
+      <c r="E244" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F244">
+        <v>2000</v>
+      </c>
+      <c r="G244" t="s">
+        <v>36</v>
+      </c>
+      <c r="H244" t="s">
+        <v>54</v>
+      </c>
+      <c r="I244" t="s">
+        <v>23</v>
+      </c>
+      <c r="J244" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A245">
+        <v>100241</v>
+      </c>
+      <c r="B245" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D245" s="5">
+        <v>20070021</v>
+      </c>
+      <c r="E245" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F245">
+        <v>9000</v>
+      </c>
+      <c r="G245" t="s">
+        <v>21</v>
+      </c>
+      <c r="H245" t="s">
+        <v>58</v>
+      </c>
+      <c r="I245" t="s">
+        <v>23</v>
+      </c>
+      <c r="J245" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A246">
+        <v>100242</v>
+      </c>
+      <c r="B246" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D246" s="5">
+        <v>20070022</v>
+      </c>
+      <c r="E246" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F246">
+        <v>9000</v>
+      </c>
+      <c r="G246" t="s">
+        <v>21</v>
+      </c>
+      <c r="H246" t="s">
+        <v>58</v>
+      </c>
+      <c r="I246" t="s">
+        <v>23</v>
+      </c>
+      <c r="J246" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A247">
+        <v>100243</v>
+      </c>
+      <c r="B247" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D247" s="5">
+        <v>20070023</v>
+      </c>
+      <c r="E247" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F247">
+        <v>9000</v>
+      </c>
+      <c r="G247" t="s">
+        <v>21</v>
+      </c>
+      <c r="H247" t="s">
+        <v>58</v>
+      </c>
+      <c r="I247" t="s">
+        <v>23</v>
+      </c>
+      <c r="J247" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A248">
+        <v>100244</v>
+      </c>
+      <c r="B248" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D248" s="5">
+        <v>20070021</v>
+      </c>
+      <c r="E248" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F248">
+        <v>7000</v>
+      </c>
+      <c r="G248" t="s">
+        <v>28</v>
+      </c>
+      <c r="H248" t="s">
+        <v>58</v>
+      </c>
+      <c r="I248" t="s">
+        <v>23</v>
+      </c>
+      <c r="J248" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A249">
+        <v>100245</v>
+      </c>
+      <c r="B249" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D249" s="5">
+        <v>20070022</v>
+      </c>
+      <c r="E249" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F249">
+        <v>7000</v>
+      </c>
+      <c r="G249" t="s">
+        <v>28</v>
+      </c>
+      <c r="H249" t="s">
+        <v>58</v>
+      </c>
+      <c r="I249" t="s">
+        <v>23</v>
+      </c>
+      <c r="J249" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A250">
+        <v>100246</v>
+      </c>
+      <c r="B250" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D250" s="5">
+        <v>20070023</v>
+      </c>
+      <c r="E250" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F250">
+        <v>7000</v>
+      </c>
+      <c r="G250" t="s">
+        <v>28</v>
+      </c>
+      <c r="H250" t="s">
+        <v>58</v>
+      </c>
+      <c r="I250" t="s">
+        <v>23</v>
+      </c>
+      <c r="J250" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A251">
+        <v>100247</v>
+      </c>
+      <c r="B251" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D251" s="5">
+        <v>20070021</v>
+      </c>
+      <c r="E251" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F251">
+        <v>5000</v>
+      </c>
+      <c r="G251" t="s">
+        <v>31</v>
+      </c>
+      <c r="H251" t="s">
+        <v>58</v>
+      </c>
+      <c r="I251" t="s">
+        <v>23</v>
+      </c>
+      <c r="J251" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A252">
+        <v>100248</v>
+      </c>
+      <c r="B252" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D252" s="5">
+        <v>20070022</v>
+      </c>
+      <c r="E252" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F252">
+        <v>5000</v>
+      </c>
+      <c r="G252" t="s">
+        <v>31</v>
+      </c>
+      <c r="H252" t="s">
+        <v>58</v>
+      </c>
+      <c r="I252" t="s">
+        <v>23</v>
+      </c>
+      <c r="J252" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A253">
+        <v>100249</v>
+      </c>
+      <c r="B253" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D253" s="5">
+        <v>20070023</v>
+      </c>
+      <c r="E253" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F253">
+        <v>5000</v>
+      </c>
+      <c r="G253" t="s">
+        <v>31</v>
+      </c>
+      <c r="H253" t="s">
+        <v>58</v>
+      </c>
+      <c r="I253" t="s">
+        <v>23</v>
+      </c>
+      <c r="J253" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A254">
+        <v>100250</v>
+      </c>
+      <c r="B254" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D254" s="5">
+        <v>20070021</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F254">
+        <v>4000</v>
+      </c>
+      <c r="G254" t="s">
+        <v>34</v>
+      </c>
+      <c r="H254" t="s">
+        <v>58</v>
+      </c>
+      <c r="I254" t="s">
+        <v>23</v>
+      </c>
+      <c r="J254" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A255">
+        <v>100251</v>
+      </c>
+      <c r="B255" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D255" s="5">
+        <v>20070022</v>
+      </c>
+      <c r="E255" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F255">
+        <v>4000</v>
+      </c>
+      <c r="G255" t="s">
+        <v>34</v>
+      </c>
+      <c r="H255" t="s">
+        <v>58</v>
+      </c>
+      <c r="I255" t="s">
+        <v>23</v>
+      </c>
+      <c r="J255" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A256">
+        <v>100252</v>
+      </c>
+      <c r="B256" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D256" s="5">
+        <v>20070023</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F256">
+        <v>4000</v>
+      </c>
+      <c r="G256" t="s">
+        <v>34</v>
+      </c>
+      <c r="H256" t="s">
+        <v>58</v>
+      </c>
+      <c r="I256" t="s">
+        <v>23</v>
+      </c>
+      <c r="J256" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A257">
+        <v>100253</v>
+      </c>
+      <c r="B257" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D257" s="5">
+        <v>20070021</v>
+      </c>
+      <c r="E257" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F257">
+        <v>2000</v>
+      </c>
+      <c r="G257" t="s">
+        <v>36</v>
+      </c>
+      <c r="H257" t="s">
+        <v>58</v>
+      </c>
+      <c r="I257" t="s">
+        <v>23</v>
+      </c>
+      <c r="J257" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A258">
+        <v>100254</v>
+      </c>
+      <c r="B258" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D258" s="5">
+        <v>20070022</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F258">
+        <v>2000</v>
+      </c>
+      <c r="G258" t="s">
+        <v>36</v>
+      </c>
+      <c r="H258" t="s">
+        <v>58</v>
+      </c>
+      <c r="I258" t="s">
+        <v>23</v>
+      </c>
+      <c r="J258" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A259">
+        <v>100255</v>
+      </c>
+      <c r="B259" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D259" s="5">
+        <v>20070023</v>
+      </c>
+      <c r="E259" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F259">
+        <v>2000</v>
+      </c>
+      <c r="G259" t="s">
+        <v>36</v>
+      </c>
+      <c r="H259" t="s">
+        <v>58</v>
+      </c>
+      <c r="I259" t="s">
+        <v>23</v>
+      </c>
+      <c r="J259" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A260">
+        <v>100256</v>
+      </c>
+      <c r="B260" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D260" s="5">
+        <v>20080021</v>
+      </c>
+      <c r="E260" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F260">
+        <v>9000</v>
+      </c>
+      <c r="G260" t="s">
+        <v>21</v>
+      </c>
+      <c r="H260" t="s">
+        <v>62</v>
+      </c>
+      <c r="I260" t="s">
+        <v>23</v>
+      </c>
+      <c r="J260" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A261">
+        <v>100257</v>
+      </c>
+      <c r="B261" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D261" s="5">
+        <v>20080022</v>
+      </c>
+      <c r="E261" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F261">
+        <v>9000</v>
+      </c>
+      <c r="G261" t="s">
+        <v>21</v>
+      </c>
+      <c r="H261" t="s">
+        <v>62</v>
+      </c>
+      <c r="I261" t="s">
+        <v>23</v>
+      </c>
+      <c r="J261" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A262">
+        <v>100258</v>
+      </c>
+      <c r="B262" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D262" s="5">
+        <v>20080023</v>
+      </c>
+      <c r="E262" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F262">
+        <v>9000</v>
+      </c>
+      <c r="G262" t="s">
+        <v>21</v>
+      </c>
+      <c r="H262" t="s">
+        <v>62</v>
+      </c>
+      <c r="I262" t="s">
+        <v>23</v>
+      </c>
+      <c r="J262" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A263">
+        <v>100259</v>
+      </c>
+      <c r="B263" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D263" s="5">
+        <v>20080021</v>
+      </c>
+      <c r="E263" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F263">
+        <v>7000</v>
+      </c>
+      <c r="G263" t="s">
+        <v>28</v>
+      </c>
+      <c r="H263" t="s">
+        <v>62</v>
+      </c>
+      <c r="I263" t="s">
+        <v>23</v>
+      </c>
+      <c r="J263" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A264">
+        <v>100260</v>
+      </c>
+      <c r="B264" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D264" s="5">
+        <v>20080022</v>
+      </c>
+      <c r="E264" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F264">
+        <v>7000</v>
+      </c>
+      <c r="G264" t="s">
+        <v>28</v>
+      </c>
+      <c r="H264" t="s">
+        <v>62</v>
+      </c>
+      <c r="I264" t="s">
+        <v>23</v>
+      </c>
+      <c r="J264" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A265">
+        <v>100261</v>
+      </c>
+      <c r="B265" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D265" s="5">
+        <v>20080023</v>
+      </c>
+      <c r="E265" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F265">
+        <v>7000</v>
+      </c>
+      <c r="G265" t="s">
+        <v>28</v>
+      </c>
+      <c r="H265" t="s">
+        <v>62</v>
+      </c>
+      <c r="I265" t="s">
+        <v>23</v>
+      </c>
+      <c r="J265" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A266">
+        <v>100262</v>
+      </c>
+      <c r="B266" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D266" s="5">
+        <v>20080021</v>
+      </c>
+      <c r="E266" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F266">
+        <v>5000</v>
+      </c>
+      <c r="G266" t="s">
+        <v>31</v>
+      </c>
+      <c r="H266" t="s">
+        <v>62</v>
+      </c>
+      <c r="I266" t="s">
+        <v>23</v>
+      </c>
+      <c r="J266" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A267">
+        <v>100263</v>
+      </c>
+      <c r="B267" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D267" s="5">
+        <v>20080022</v>
+      </c>
+      <c r="E267" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F267">
+        <v>5000</v>
+      </c>
+      <c r="G267" t="s">
+        <v>31</v>
+      </c>
+      <c r="H267" t="s">
+        <v>62</v>
+      </c>
+      <c r="I267" t="s">
+        <v>23</v>
+      </c>
+      <c r="J267" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A268">
+        <v>100264</v>
+      </c>
+      <c r="B268" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D268" s="5">
+        <v>20080023</v>
+      </c>
+      <c r="E268" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F268">
+        <v>5000</v>
+      </c>
+      <c r="G268" t="s">
+        <v>31</v>
+      </c>
+      <c r="H268" t="s">
+        <v>62</v>
+      </c>
+      <c r="I268" t="s">
+        <v>23</v>
+      </c>
+      <c r="J268" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A269">
+        <v>100265</v>
+      </c>
+      <c r="B269" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D269" s="5">
+        <v>20080021</v>
+      </c>
+      <c r="E269" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F269">
+        <v>4000</v>
+      </c>
+      <c r="G269" t="s">
+        <v>34</v>
+      </c>
+      <c r="H269" t="s">
+        <v>62</v>
+      </c>
+      <c r="I269" t="s">
+        <v>23</v>
+      </c>
+      <c r="J269" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A270">
+        <v>100266</v>
+      </c>
+      <c r="B270" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D270" s="5">
+        <v>20080022</v>
+      </c>
+      <c r="E270" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F270">
+        <v>4000</v>
+      </c>
+      <c r="G270" t="s">
+        <v>34</v>
+      </c>
+      <c r="H270" t="s">
+        <v>62</v>
+      </c>
+      <c r="I270" t="s">
+        <v>23</v>
+      </c>
+      <c r="J270" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A271">
+        <v>100267</v>
+      </c>
+      <c r="B271" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D271" s="5">
+        <v>20080023</v>
+      </c>
+      <c r="E271" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F271">
+        <v>4000</v>
+      </c>
+      <c r="G271" t="s">
+        <v>34</v>
+      </c>
+      <c r="H271" t="s">
+        <v>62</v>
+      </c>
+      <c r="I271" t="s">
+        <v>23</v>
+      </c>
+      <c r="J271" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A272">
+        <v>100268</v>
+      </c>
+      <c r="B272" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D272" s="5">
+        <v>20080021</v>
+      </c>
+      <c r="E272" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F272">
+        <v>2000</v>
+      </c>
+      <c r="G272" t="s">
+        <v>36</v>
+      </c>
+      <c r="H272" t="s">
+        <v>62</v>
+      </c>
+      <c r="I272" t="s">
+        <v>23</v>
+      </c>
+      <c r="J272" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A273">
+        <v>100269</v>
+      </c>
+      <c r="B273" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D273" s="5">
+        <v>20080022</v>
+      </c>
+      <c r="E273" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F273">
+        <v>2000</v>
+      </c>
+      <c r="G273" t="s">
+        <v>36</v>
+      </c>
+      <c r="H273" t="s">
+        <v>62</v>
+      </c>
+      <c r="I273" t="s">
+        <v>23</v>
+      </c>
+      <c r="J273" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A274">
+        <v>100270</v>
+      </c>
+      <c r="B274" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D274" s="5">
+        <v>20080023</v>
+      </c>
+      <c r="E274" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F274">
+        <v>2000</v>
+      </c>
+      <c r="G274" t="s">
+        <v>36</v>
+      </c>
+      <c r="H274" t="s">
+        <v>62</v>
+      </c>
+      <c r="I274" t="s">
+        <v>23</v>
+      </c>
+      <c r="J274" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A275">
+        <v>100271</v>
+      </c>
+      <c r="B275" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D275" s="5">
+        <v>20090021</v>
+      </c>
+      <c r="E275" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F275">
+        <v>9000</v>
+      </c>
+      <c r="G275" t="s">
+        <v>21</v>
+      </c>
+      <c r="H275" t="s">
+        <v>66</v>
+      </c>
+      <c r="I275" t="s">
+        <v>23</v>
+      </c>
+      <c r="J275" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A276">
+        <v>100272</v>
+      </c>
+      <c r="B276" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D276" s="5">
+        <v>20090022</v>
+      </c>
+      <c r="E276" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F276">
+        <v>9000</v>
+      </c>
+      <c r="G276" t="s">
+        <v>21</v>
+      </c>
+      <c r="H276" t="s">
+        <v>66</v>
+      </c>
+      <c r="I276" t="s">
+        <v>23</v>
+      </c>
+      <c r="J276" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A277">
+        <v>100273</v>
+      </c>
+      <c r="B277" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D277" s="5">
+        <v>20090023</v>
+      </c>
+      <c r="E277" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F277">
+        <v>9000</v>
+      </c>
+      <c r="G277" t="s">
+        <v>21</v>
+      </c>
+      <c r="H277" t="s">
+        <v>66</v>
+      </c>
+      <c r="I277" t="s">
+        <v>23</v>
+      </c>
+      <c r="J277" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A278">
+        <v>100274</v>
+      </c>
+      <c r="B278" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D278" s="5">
+        <v>20090021</v>
+      </c>
+      <c r="E278" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F278">
+        <v>7000</v>
+      </c>
+      <c r="G278" t="s">
+        <v>28</v>
+      </c>
+      <c r="H278" t="s">
+        <v>66</v>
+      </c>
+      <c r="I278" t="s">
+        <v>23</v>
+      </c>
+      <c r="J278" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A279">
+        <v>100275</v>
+      </c>
+      <c r="B279" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D279" s="5">
+        <v>20090022</v>
+      </c>
+      <c r="E279" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F279">
+        <v>7000</v>
+      </c>
+      <c r="G279" t="s">
+        <v>28</v>
+      </c>
+      <c r="H279" t="s">
+        <v>66</v>
+      </c>
+      <c r="I279" t="s">
+        <v>23</v>
+      </c>
+      <c r="J279" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A280">
+        <v>100276</v>
+      </c>
+      <c r="B280" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D280" s="5">
+        <v>20090023</v>
+      </c>
+      <c r="E280" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F280">
+        <v>7000</v>
+      </c>
+      <c r="G280" t="s">
+        <v>28</v>
+      </c>
+      <c r="H280" t="s">
+        <v>66</v>
+      </c>
+      <c r="I280" t="s">
+        <v>23</v>
+      </c>
+      <c r="J280" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A281">
+        <v>100277</v>
+      </c>
+      <c r="B281" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D281" s="5">
+        <v>20090021</v>
+      </c>
+      <c r="E281" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F281">
+        <v>5000</v>
+      </c>
+      <c r="G281" t="s">
+        <v>31</v>
+      </c>
+      <c r="H281" t="s">
+        <v>66</v>
+      </c>
+      <c r="I281" t="s">
+        <v>23</v>
+      </c>
+      <c r="J281" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A282">
+        <v>100278</v>
+      </c>
+      <c r="B282" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D282" s="5">
+        <v>20090022</v>
+      </c>
+      <c r="E282" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F282">
+        <v>5000</v>
+      </c>
+      <c r="G282" t="s">
+        <v>31</v>
+      </c>
+      <c r="H282" t="s">
+        <v>66</v>
+      </c>
+      <c r="I282" t="s">
+        <v>23</v>
+      </c>
+      <c r="J282" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A283">
+        <v>100279</v>
+      </c>
+      <c r="B283" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D283" s="5">
+        <v>20090023</v>
+      </c>
+      <c r="E283" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F283">
+        <v>5000</v>
+      </c>
+      <c r="G283" t="s">
+        <v>31</v>
+      </c>
+      <c r="H283" t="s">
+        <v>66</v>
+      </c>
+      <c r="I283" t="s">
+        <v>23</v>
+      </c>
+      <c r="J283" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A284">
+        <v>100280</v>
+      </c>
+      <c r="B284" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D284" s="5">
+        <v>20090021</v>
+      </c>
+      <c r="E284" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F284">
+        <v>4000</v>
+      </c>
+      <c r="G284" t="s">
+        <v>34</v>
+      </c>
+      <c r="H284" t="s">
+        <v>66</v>
+      </c>
+      <c r="I284" t="s">
+        <v>23</v>
+      </c>
+      <c r="J284" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A285">
+        <v>100281</v>
+      </c>
+      <c r="B285" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D285" s="5">
+        <v>20090022</v>
+      </c>
+      <c r="E285" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F285">
+        <v>4000</v>
+      </c>
+      <c r="G285" t="s">
+        <v>34</v>
+      </c>
+      <c r="H285" t="s">
+        <v>66</v>
+      </c>
+      <c r="I285" t="s">
+        <v>23</v>
+      </c>
+      <c r="J285" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A286">
+        <v>100282</v>
+      </c>
+      <c r="B286" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D286" s="5">
+        <v>20090023</v>
+      </c>
+      <c r="E286" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F286">
+        <v>4000</v>
+      </c>
+      <c r="G286" t="s">
+        <v>34</v>
+      </c>
+      <c r="H286" t="s">
+        <v>66</v>
+      </c>
+      <c r="I286" t="s">
+        <v>23</v>
+      </c>
+      <c r="J286" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A287">
+        <v>100283</v>
+      </c>
+      <c r="B287" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D287" s="5">
+        <v>20090021</v>
+      </c>
+      <c r="E287" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F287">
+        <v>2000</v>
+      </c>
+      <c r="G287" t="s">
+        <v>36</v>
+      </c>
+      <c r="H287" t="s">
+        <v>66</v>
+      </c>
+      <c r="I287" t="s">
+        <v>23</v>
+      </c>
+      <c r="J287" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A288">
+        <v>100284</v>
+      </c>
+      <c r="B288" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D288" s="5">
+        <v>20090022</v>
+      </c>
+      <c r="E288" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F288">
+        <v>2000</v>
+      </c>
+      <c r="G288" t="s">
+        <v>36</v>
+      </c>
+      <c r="H288" t="s">
+        <v>66</v>
+      </c>
+      <c r="I288" t="s">
+        <v>23</v>
+      </c>
+      <c r="J288" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A289">
+        <v>100285</v>
+      </c>
+      <c r="B289" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D289" s="5">
+        <v>20090023</v>
+      </c>
+      <c r="E289" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F289">
+        <v>2000</v>
+      </c>
+      <c r="G289" t="s">
+        <v>36</v>
+      </c>
+      <c r="H289" t="s">
+        <v>66</v>
+      </c>
+      <c r="I289" t="s">
+        <v>23</v>
+      </c>
+      <c r="J289" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A290">
+        <v>100286</v>
+      </c>
+      <c r="B290" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D290" s="5">
+        <v>20120021</v>
+      </c>
+      <c r="E290" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F290">
+        <v>9000</v>
+      </c>
+      <c r="G290" t="s">
+        <v>21</v>
+      </c>
+      <c r="H290" t="s">
+        <v>70</v>
+      </c>
+      <c r="I290" t="s">
+        <v>23</v>
+      </c>
+      <c r="J290" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A291">
+        <v>100287</v>
+      </c>
+      <c r="B291" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D291" s="5">
+        <v>20120022</v>
+      </c>
+      <c r="E291" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F291">
+        <v>9000</v>
+      </c>
+      <c r="G291" t="s">
+        <v>21</v>
+      </c>
+      <c r="H291" t="s">
+        <v>70</v>
+      </c>
+      <c r="I291" t="s">
+        <v>23</v>
+      </c>
+      <c r="J291" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A292">
+        <v>100288</v>
+      </c>
+      <c r="B292" s="4">
+        <v>10099</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D292" s="5">
+        <v>20120023</v>
+      </c>
+      <c r="E292" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F292">
+        <v>9000</v>
+      </c>
+      <c r="G292" t="s">
+        <v>21</v>
+      </c>
+      <c r="H292" t="s">
+        <v>70</v>
+      </c>
+      <c r="I292" t="s">
+        <v>23</v>
+      </c>
+      <c r="J292" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A293">
+        <v>100289</v>
+      </c>
+      <c r="B293" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D293" s="5">
+        <v>20120021</v>
+      </c>
+      <c r="E293" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F293">
+        <v>7000</v>
+      </c>
+      <c r="G293" t="s">
+        <v>28</v>
+      </c>
+      <c r="H293" t="s">
+        <v>70</v>
+      </c>
+      <c r="I293" t="s">
+        <v>23</v>
+      </c>
+      <c r="J293" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A294">
+        <v>100290</v>
+      </c>
+      <c r="B294" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D294" s="5">
+        <v>20120022</v>
+      </c>
+      <c r="E294" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F294">
+        <v>7000</v>
+      </c>
+      <c r="G294" t="s">
+        <v>28</v>
+      </c>
+      <c r="H294" t="s">
+        <v>70</v>
+      </c>
+      <c r="I294" t="s">
+        <v>23</v>
+      </c>
+      <c r="J294" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A295">
+        <v>100291</v>
+      </c>
+      <c r="B295" s="4">
+        <v>10075</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D295" s="5">
+        <v>20120023</v>
+      </c>
+      <c r="E295" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F295">
+        <v>7000</v>
+      </c>
+      <c r="G295" t="s">
+        <v>28</v>
+      </c>
+      <c r="H295" t="s">
+        <v>70</v>
+      </c>
+      <c r="I295" t="s">
+        <v>23</v>
+      </c>
+      <c r="J295" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A296">
+        <v>100292</v>
+      </c>
+      <c r="B296" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D296" s="5">
+        <v>20120021</v>
+      </c>
+      <c r="E296" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F296">
+        <v>5000</v>
+      </c>
+      <c r="G296" t="s">
+        <v>31</v>
+      </c>
+      <c r="H296" t="s">
+        <v>70</v>
+      </c>
+      <c r="I296" t="s">
+        <v>23</v>
+      </c>
+      <c r="J296" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A297">
+        <v>100293</v>
+      </c>
+      <c r="B297" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D297" s="5">
+        <v>20120022</v>
+      </c>
+      <c r="E297" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F297">
+        <v>5000</v>
+      </c>
+      <c r="G297" t="s">
+        <v>31</v>
+      </c>
+      <c r="H297" t="s">
+        <v>70</v>
+      </c>
+      <c r="I297" t="s">
+        <v>23</v>
+      </c>
+      <c r="J297" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A298">
+        <v>100294</v>
+      </c>
+      <c r="B298" s="4">
+        <v>10050</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D298" s="5">
+        <v>20120023</v>
+      </c>
+      <c r="E298" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F298">
+        <v>5000</v>
+      </c>
+      <c r="G298" t="s">
+        <v>31</v>
+      </c>
+      <c r="H298" t="s">
+        <v>70</v>
+      </c>
+      <c r="I298" t="s">
+        <v>23</v>
+      </c>
+      <c r="J298" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A299">
+        <v>100295</v>
+      </c>
+      <c r="B299" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D299" s="5">
+        <v>20120021</v>
+      </c>
+      <c r="E299" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F299">
+        <v>4000</v>
+      </c>
+      <c r="G299" t="s">
+        <v>34</v>
+      </c>
+      <c r="H299" t="s">
+        <v>70</v>
+      </c>
+      <c r="I299" t="s">
+        <v>23</v>
+      </c>
+      <c r="J299" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A300">
+        <v>100296</v>
+      </c>
+      <c r="B300" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D300" s="5">
+        <v>20120022</v>
+      </c>
+      <c r="E300" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F300">
+        <v>4000</v>
+      </c>
+      <c r="G300" t="s">
+        <v>34</v>
+      </c>
+      <c r="H300" t="s">
+        <v>70</v>
+      </c>
+      <c r="I300" t="s">
+        <v>23</v>
+      </c>
+      <c r="J300" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A301">
+        <v>100297</v>
+      </c>
+      <c r="B301" s="4">
+        <v>10025</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D301" s="5">
+        <v>20120023</v>
+      </c>
+      <c r="E301" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F301">
+        <v>4000</v>
+      </c>
+      <c r="G301" t="s">
+        <v>34</v>
+      </c>
+      <c r="H301" t="s">
+        <v>70</v>
+      </c>
+      <c r="I301" t="s">
+        <v>23</v>
+      </c>
+      <c r="J301" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A302">
+        <v>100298</v>
+      </c>
+      <c r="B302" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D302" s="5">
+        <v>20120021</v>
+      </c>
+      <c r="E302" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F302">
+        <v>2000</v>
+      </c>
+      <c r="G302" t="s">
+        <v>36</v>
+      </c>
+      <c r="H302" t="s">
+        <v>70</v>
+      </c>
+      <c r="I302" t="s">
+        <v>23</v>
+      </c>
+      <c r="J302" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A303">
+        <v>100299</v>
+      </c>
+      <c r="B303" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D303" s="5">
+        <v>20120022</v>
+      </c>
+      <c r="E303" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F303">
+        <v>2000</v>
+      </c>
+      <c r="G303" t="s">
+        <v>36</v>
+      </c>
+      <c r="H303" t="s">
+        <v>70</v>
+      </c>
+      <c r="I303" t="s">
+        <v>23</v>
+      </c>
+      <c r="J303" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A304">
+        <v>100300</v>
+      </c>
+      <c r="B304" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D304" s="5">
+        <v>20120023</v>
+      </c>
+      <c r="E304" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F304">
+        <v>2000</v>
+      </c>
+      <c r="G304" t="s">
+        <v>36</v>
+      </c>
+      <c r="H304" t="s">
+        <v>70</v>
+      </c>
+      <c r="I304" t="s">
+        <v>23</v>
+      </c>
+      <c r="J304" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/table/resources/sample/RobotAction_Bet.xlsx
+++ b/table/resources/sample/RobotAction_Bet.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\bet\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27DFED2-39CB-4FE8-AE94-0AC1A87B2586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BetRobot" sheetId="1" r:id="rId1"/>
@@ -33,19 +27,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -54,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -63,14 +55,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -79,7 +70,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -89,14 +79,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -105,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -115,14 +103,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -131,7 +118,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -141,14 +127,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -157,7 +142,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -166,14 +150,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -182,7 +165,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -196,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="73">
   <si>
     <t>序列</t>
   </si>
@@ -420,8 +402,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -433,45 +421,170 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,54 +593,240 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -535,26 +834,268 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -582,159 +1123,90 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2 2" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -745,7 +1217,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -773,40 +1245,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1056,14 +1642,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J304"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J154"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="4" width="12.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
@@ -1074,7 +1660,7 @@
     <col min="10" max="10" width="28.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1102,7 +1688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1130,7 +1716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1158,13 +1744,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>100001</v>
       </c>
@@ -1196,7 +1782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>100002</v>
       </c>
@@ -1228,7 +1814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>100003</v>
       </c>
@@ -1260,7 +1846,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>100004</v>
       </c>
@@ -1292,7 +1878,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>100005</v>
       </c>
@@ -1324,7 +1910,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>100006</v>
       </c>
@@ -1356,7 +1942,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>100007</v>
       </c>
@@ -1388,7 +1974,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>100008</v>
       </c>
@@ -1420,7 +2006,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>100009</v>
       </c>
@@ -1452,7 +2038,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>100010</v>
       </c>
@@ -1484,7 +2070,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>100011</v>
       </c>
@@ -1516,7 +2102,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>100012</v>
       </c>
@@ -1548,7 +2134,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>100013</v>
       </c>
@@ -1580,7 +2166,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>100014</v>
       </c>
@@ -1612,7 +2198,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>100015</v>
       </c>
@@ -1644,7 +2230,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>100016</v>
       </c>
@@ -1676,7 +2262,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>100017</v>
       </c>
@@ -1708,7 +2294,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>100018</v>
       </c>
@@ -1740,7 +2326,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>100019</v>
       </c>
@@ -1772,7 +2358,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>100020</v>
       </c>
@@ -1804,7 +2390,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>100021</v>
       </c>
@@ -1836,7 +2422,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>100022</v>
       </c>
@@ -1868,7 +2454,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>100023</v>
       </c>
@@ -1900,7 +2486,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>100024</v>
       </c>
@@ -1932,7 +2518,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>100025</v>
       </c>
@@ -1964,7 +2550,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>100026</v>
       </c>
@@ -1996,7 +2582,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>100027</v>
       </c>
@@ -2028,7 +2614,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>100028</v>
       </c>
@@ -2060,7 +2646,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33">
         <v>100029</v>
       </c>
@@ -2092,7 +2678,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>100030</v>
       </c>
@@ -2124,7 +2710,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>100031</v>
       </c>
@@ -2156,7 +2742,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>100032</v>
       </c>
@@ -2188,7 +2774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>100033</v>
       </c>
@@ -2220,7 +2806,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>100034</v>
       </c>
@@ -2252,7 +2838,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>100035</v>
       </c>
@@ -2284,7 +2870,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:10">
       <c r="A40">
         <v>100036</v>
       </c>
@@ -2316,7 +2902,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:10">
       <c r="A41">
         <v>100037</v>
       </c>
@@ -2348,7 +2934,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:10">
       <c r="A42">
         <v>100038</v>
       </c>
@@ -2380,7 +2966,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:10">
       <c r="A43">
         <v>100039</v>
       </c>
@@ -2412,7 +2998,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:10">
       <c r="A44">
         <v>100040</v>
       </c>
@@ -2444,7 +3030,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:10">
       <c r="A45">
         <v>100041</v>
       </c>
@@ -2476,7 +3062,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:10">
       <c r="A46">
         <v>100042</v>
       </c>
@@ -2508,7 +3094,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:10">
       <c r="A47">
         <v>100043</v>
       </c>
@@ -2540,7 +3126,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:10">
       <c r="A48">
         <v>100044</v>
       </c>
@@ -2572,7 +3158,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:10">
       <c r="A49">
         <v>100045</v>
       </c>
@@ -2604,7 +3190,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:10">
       <c r="A50">
         <v>100046</v>
       </c>
@@ -2636,7 +3222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:10">
       <c r="A51">
         <v>100047</v>
       </c>
@@ -2668,7 +3254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:10">
       <c r="A52">
         <v>100048</v>
       </c>
@@ -2700,7 +3286,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:10">
       <c r="A53">
         <v>100049</v>
       </c>
@@ -2732,7 +3318,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:10">
       <c r="A54">
         <v>100050</v>
       </c>
@@ -2764,7 +3350,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:10">
       <c r="A55">
         <v>100051</v>
       </c>
@@ -2796,7 +3382,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:10">
       <c r="A56">
         <v>100052</v>
       </c>
@@ -2828,7 +3414,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:10">
       <c r="A57">
         <v>100053</v>
       </c>
@@ -2860,7 +3446,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:10">
       <c r="A58">
         <v>100054</v>
       </c>
@@ -2892,7 +3478,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:10">
       <c r="A59">
         <v>100055</v>
       </c>
@@ -2924,7 +3510,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:10">
       <c r="A60">
         <v>100056</v>
       </c>
@@ -2956,7 +3542,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>100057</v>
       </c>
@@ -2988,7 +3574,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:10">
       <c r="A62">
         <v>100058</v>
       </c>
@@ -3020,7 +3606,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>100059</v>
       </c>
@@ -3052,7 +3638,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>100060</v>
       </c>
@@ -3084,7 +3670,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:10">
       <c r="A65">
         <v>100061</v>
       </c>
@@ -3116,7 +3702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:10">
       <c r="A66">
         <v>100062</v>
       </c>
@@ -3148,7 +3734,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:10">
       <c r="A67">
         <v>100063</v>
       </c>
@@ -3180,7 +3766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:10">
       <c r="A68">
         <v>100064</v>
       </c>
@@ -3212,7 +3798,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:10">
       <c r="A69">
         <v>100065</v>
       </c>
@@ -3244,7 +3830,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:10">
       <c r="A70">
         <v>100066</v>
       </c>
@@ -3276,7 +3862,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:10">
       <c r="A71">
         <v>100067</v>
       </c>
@@ -3308,7 +3894,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:10">
       <c r="A72">
         <v>100068</v>
       </c>
@@ -3340,7 +3926,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:10">
       <c r="A73">
         <v>100069</v>
       </c>
@@ -3372,7 +3958,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:10">
       <c r="A74">
         <v>100070</v>
       </c>
@@ -3404,7 +3990,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:10">
       <c r="A75">
         <v>100071</v>
       </c>
@@ -3436,7 +4022,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:10">
       <c r="A76">
         <v>100072</v>
       </c>
@@ -3468,7 +4054,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:10">
       <c r="A77">
         <v>100073</v>
       </c>
@@ -3500,7 +4086,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:10">
       <c r="A78">
         <v>100074</v>
       </c>
@@ -3532,7 +4118,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:10">
       <c r="A79">
         <v>100075</v>
       </c>
@@ -3564,7 +4150,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:10">
       <c r="A80">
         <v>100076</v>
       </c>
@@ -3596,7 +4182,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:10">
       <c r="A81">
         <v>100077</v>
       </c>
@@ -3628,7 +4214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:10">
       <c r="A82">
         <v>100078</v>
       </c>
@@ -3660,7 +4246,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:10">
       <c r="A83">
         <v>100079</v>
       </c>
@@ -3692,7 +4278,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:10">
       <c r="A84">
         <v>100080</v>
       </c>
@@ -3724,7 +4310,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:10">
       <c r="A85">
         <v>100081</v>
       </c>
@@ -3756,7 +4342,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:10">
       <c r="A86">
         <v>100082</v>
       </c>
@@ -3788,7 +4374,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:10">
       <c r="A87">
         <v>100083</v>
       </c>
@@ -3820,7 +4406,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:10">
       <c r="A88">
         <v>100084</v>
       </c>
@@ -3852,7 +4438,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:10">
       <c r="A89">
         <v>100085</v>
       </c>
@@ -3884,7 +4470,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:10">
       <c r="A90">
         <v>100086</v>
       </c>
@@ -3916,7 +4502,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:10">
       <c r="A91">
         <v>100087</v>
       </c>
@@ -3948,7 +4534,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:10">
       <c r="A92">
         <v>100088</v>
       </c>
@@ -3980,7 +4566,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:10">
       <c r="A93">
         <v>100089</v>
       </c>
@@ -4012,7 +4598,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:10">
       <c r="A94">
         <v>100090</v>
       </c>
@@ -4044,7 +4630,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:10">
       <c r="A95">
         <v>100091</v>
       </c>
@@ -4076,7 +4662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:10">
       <c r="A96">
         <v>100092</v>
       </c>
@@ -4108,7 +4694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:10">
       <c r="A97">
         <v>100093</v>
       </c>
@@ -4140,7 +4726,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:10">
       <c r="A98">
         <v>100094</v>
       </c>
@@ -4172,7 +4758,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:10">
       <c r="A99">
         <v>100095</v>
       </c>
@@ -4204,7 +4790,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:10">
       <c r="A100">
         <v>100096</v>
       </c>
@@ -4236,7 +4822,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:10">
       <c r="A101">
         <v>100097</v>
       </c>
@@ -4268,7 +4854,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:10">
       <c r="A102">
         <v>100098</v>
       </c>
@@ -4300,7 +4886,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:10">
       <c r="A103">
         <v>100099</v>
       </c>
@@ -4332,7 +4918,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:10">
       <c r="A104">
         <v>100100</v>
       </c>
@@ -4364,7 +4950,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:10">
       <c r="A105">
         <v>100101</v>
       </c>
@@ -4396,7 +4982,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:10">
       <c r="A106">
         <v>100102</v>
       </c>
@@ -4428,7 +5014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:10">
       <c r="A107">
         <v>100103</v>
       </c>
@@ -4460,7 +5046,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:10">
       <c r="A108">
         <v>100104</v>
       </c>
@@ -4492,7 +5078,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:10">
       <c r="A109">
         <v>100105</v>
       </c>
@@ -4524,7 +5110,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:10">
       <c r="A110">
         <v>100106</v>
       </c>
@@ -4556,7 +5142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:10">
       <c r="A111">
         <v>100107</v>
       </c>
@@ -4588,7 +5174,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:10">
       <c r="A112">
         <v>100108</v>
       </c>
@@ -4620,7 +5206,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:10">
       <c r="A113">
         <v>100109</v>
       </c>
@@ -4652,7 +5238,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:10">
       <c r="A114">
         <v>100110</v>
       </c>
@@ -4684,7 +5270,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:10">
       <c r="A115">
         <v>100111</v>
       </c>
@@ -4716,7 +5302,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:10">
       <c r="A116">
         <v>100112</v>
       </c>
@@ -4748,7 +5334,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:10">
       <c r="A117">
         <v>100113</v>
       </c>
@@ -4780,7 +5366,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:10">
       <c r="A118">
         <v>100114</v>
       </c>
@@ -4812,7 +5398,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:10">
       <c r="A119">
         <v>100115</v>
       </c>
@@ -4844,7 +5430,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:10">
       <c r="A120">
         <v>100116</v>
       </c>
@@ -4876,7 +5462,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:10">
       <c r="A121">
         <v>100117</v>
       </c>
@@ -4908,7 +5494,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:10">
       <c r="A122">
         <v>100118</v>
       </c>
@@ -4940,7 +5526,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:10">
       <c r="A123">
         <v>100119</v>
       </c>
@@ -4972,7 +5558,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:10">
       <c r="A124">
         <v>100120</v>
       </c>
@@ -5004,7 +5590,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:10">
       <c r="A125">
         <v>100121</v>
       </c>
@@ -5036,7 +5622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:10">
       <c r="A126">
         <v>100122</v>
       </c>
@@ -5068,7 +5654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:10">
       <c r="A127">
         <v>100123</v>
       </c>
@@ -5100,7 +5686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:10">
       <c r="A128">
         <v>100124</v>
       </c>
@@ -5132,7 +5718,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:10">
       <c r="A129">
         <v>100125</v>
       </c>
@@ -5164,7 +5750,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:10">
       <c r="A130">
         <v>100126</v>
       </c>
@@ -5196,7 +5782,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:10">
       <c r="A131">
         <v>100127</v>
       </c>
@@ -5228,7 +5814,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:10">
       <c r="A132">
         <v>100128</v>
       </c>
@@ -5260,7 +5846,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:10">
       <c r="A133">
         <v>100129</v>
       </c>
@@ -5292,7 +5878,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:10">
       <c r="A134">
         <v>100130</v>
       </c>
@@ -5324,7 +5910,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:10">
       <c r="A135">
         <v>100131</v>
       </c>
@@ -5356,7 +5942,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:10">
       <c r="A136">
         <v>100132</v>
       </c>
@@ -5388,7 +5974,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:10">
       <c r="A137">
         <v>100133</v>
       </c>
@@ -5420,7 +6006,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:10">
       <c r="A138">
         <v>100134</v>
       </c>
@@ -5452,7 +6038,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:10">
       <c r="A139">
         <v>100135</v>
       </c>
@@ -5484,7 +6070,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:10">
       <c r="A140">
         <v>100136</v>
       </c>
@@ -5516,7 +6102,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:10">
       <c r="A141">
         <v>100137</v>
       </c>
@@ -5548,7 +6134,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:10">
       <c r="A142">
         <v>100138</v>
       </c>
@@ -5580,7 +6166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:10">
       <c r="A143">
         <v>100139</v>
       </c>
@@ -5612,7 +6198,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:10">
       <c r="A144">
         <v>100140</v>
       </c>
@@ -5644,7 +6230,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:10">
       <c r="A145">
         <v>100141</v>
       </c>
@@ -5676,7 +6262,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:10">
       <c r="A146">
         <v>100142</v>
       </c>
@@ -5708,7 +6294,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:10">
       <c r="A147">
         <v>100143</v>
       </c>
@@ -5740,7 +6326,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:10">
       <c r="A148">
         <v>100144</v>
       </c>
@@ -5772,7 +6358,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:10">
       <c r="A149">
         <v>100145</v>
       </c>
@@ -5804,7 +6390,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:10">
       <c r="A150">
         <v>100146</v>
       </c>
@@ -5836,7 +6422,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:10">
       <c r="A151">
         <v>100147</v>
       </c>
@@ -5868,7 +6454,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:10">
       <c r="A152">
         <v>100148</v>
       </c>
@@ -5900,7 +6486,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:10">
       <c r="A153">
         <v>100149</v>
       </c>
@@ -5932,7 +6518,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:10">
       <c r="A154">
         <v>100150</v>
       </c>
@@ -5964,4809 +6550,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A155">
-        <v>100151</v>
-      </c>
-      <c r="B155" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D155" s="5">
-        <v>20040021</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F155">
-        <v>9000</v>
-      </c>
-      <c r="G155" t="s">
-        <v>21</v>
-      </c>
-      <c r="H155" t="s">
-        <v>22</v>
-      </c>
-      <c r="I155" t="s">
-        <v>23</v>
-      </c>
-      <c r="J155" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A156">
-        <v>100152</v>
-      </c>
-      <c r="B156" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D156" s="5">
-        <v>20040022</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F156">
-        <v>9000</v>
-      </c>
-      <c r="G156" t="s">
-        <v>21</v>
-      </c>
-      <c r="H156" t="s">
-        <v>22</v>
-      </c>
-      <c r="I156" t="s">
-        <v>23</v>
-      </c>
-      <c r="J156" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A157">
-        <v>100153</v>
-      </c>
-      <c r="B157" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D157" s="5">
-        <v>20040023</v>
-      </c>
-      <c r="E157" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F157">
-        <v>9000</v>
-      </c>
-      <c r="G157" t="s">
-        <v>21</v>
-      </c>
-      <c r="H157" t="s">
-        <v>22</v>
-      </c>
-      <c r="I157" t="s">
-        <v>23</v>
-      </c>
-      <c r="J157" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A158">
-        <v>100154</v>
-      </c>
-      <c r="B158" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D158" s="5">
-        <v>20040021</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F158">
-        <v>7000</v>
-      </c>
-      <c r="G158" t="s">
-        <v>28</v>
-      </c>
-      <c r="H158" t="s">
-        <v>22</v>
-      </c>
-      <c r="I158" t="s">
-        <v>23</v>
-      </c>
-      <c r="J158" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A159">
-        <v>100155</v>
-      </c>
-      <c r="B159" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D159" s="5">
-        <v>20040022</v>
-      </c>
-      <c r="E159" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F159">
-        <v>7000</v>
-      </c>
-      <c r="G159" t="s">
-        <v>28</v>
-      </c>
-      <c r="H159" t="s">
-        <v>22</v>
-      </c>
-      <c r="I159" t="s">
-        <v>23</v>
-      </c>
-      <c r="J159" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A160">
-        <v>100156</v>
-      </c>
-      <c r="B160" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D160" s="5">
-        <v>20040023</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F160">
-        <v>7000</v>
-      </c>
-      <c r="G160" t="s">
-        <v>28</v>
-      </c>
-      <c r="H160" t="s">
-        <v>22</v>
-      </c>
-      <c r="I160" t="s">
-        <v>23</v>
-      </c>
-      <c r="J160" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A161">
-        <v>100157</v>
-      </c>
-      <c r="B161" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D161" s="5">
-        <v>20040021</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F161">
-        <v>5000</v>
-      </c>
-      <c r="G161" t="s">
-        <v>31</v>
-      </c>
-      <c r="H161" t="s">
-        <v>22</v>
-      </c>
-      <c r="I161" t="s">
-        <v>23</v>
-      </c>
-      <c r="J161" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A162">
-        <v>100158</v>
-      </c>
-      <c r="B162" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D162" s="5">
-        <v>20040022</v>
-      </c>
-      <c r="E162" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F162">
-        <v>5000</v>
-      </c>
-      <c r="G162" t="s">
-        <v>31</v>
-      </c>
-      <c r="H162" t="s">
-        <v>22</v>
-      </c>
-      <c r="I162" t="s">
-        <v>23</v>
-      </c>
-      <c r="J162" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A163">
-        <v>100159</v>
-      </c>
-      <c r="B163" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D163" s="5">
-        <v>20040023</v>
-      </c>
-      <c r="E163" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F163">
-        <v>5000</v>
-      </c>
-      <c r="G163" t="s">
-        <v>31</v>
-      </c>
-      <c r="H163" t="s">
-        <v>22</v>
-      </c>
-      <c r="I163" t="s">
-        <v>23</v>
-      </c>
-      <c r="J163" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A164">
-        <v>100160</v>
-      </c>
-      <c r="B164" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D164" s="5">
-        <v>20040021</v>
-      </c>
-      <c r="E164" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F164">
-        <v>4000</v>
-      </c>
-      <c r="G164" t="s">
-        <v>34</v>
-      </c>
-      <c r="H164" t="s">
-        <v>22</v>
-      </c>
-      <c r="I164" t="s">
-        <v>23</v>
-      </c>
-      <c r="J164" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A165">
-        <v>100161</v>
-      </c>
-      <c r="B165" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D165" s="5">
-        <v>20040022</v>
-      </c>
-      <c r="E165" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F165">
-        <v>4000</v>
-      </c>
-      <c r="G165" t="s">
-        <v>34</v>
-      </c>
-      <c r="H165" t="s">
-        <v>22</v>
-      </c>
-      <c r="I165" t="s">
-        <v>23</v>
-      </c>
-      <c r="J165" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A166">
-        <v>100162</v>
-      </c>
-      <c r="B166" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D166" s="5">
-        <v>20040023</v>
-      </c>
-      <c r="E166" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F166">
-        <v>4000</v>
-      </c>
-      <c r="G166" t="s">
-        <v>34</v>
-      </c>
-      <c r="H166" t="s">
-        <v>22</v>
-      </c>
-      <c r="I166" t="s">
-        <v>23</v>
-      </c>
-      <c r="J166" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A167">
-        <v>100163</v>
-      </c>
-      <c r="B167" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D167" s="5">
-        <v>20040021</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F167">
-        <v>2000</v>
-      </c>
-      <c r="G167" t="s">
-        <v>36</v>
-      </c>
-      <c r="H167" t="s">
-        <v>22</v>
-      </c>
-      <c r="I167" t="s">
-        <v>23</v>
-      </c>
-      <c r="J167" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A168">
-        <v>100164</v>
-      </c>
-      <c r="B168" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D168" s="5">
-        <v>20040022</v>
-      </c>
-      <c r="E168" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F168">
-        <v>2000</v>
-      </c>
-      <c r="G168" t="s">
-        <v>36</v>
-      </c>
-      <c r="H168" t="s">
-        <v>22</v>
-      </c>
-      <c r="I168" t="s">
-        <v>23</v>
-      </c>
-      <c r="J168" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A169">
-        <v>100165</v>
-      </c>
-      <c r="B169" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D169" s="5">
-        <v>20040023</v>
-      </c>
-      <c r="E169" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F169">
-        <v>2000</v>
-      </c>
-      <c r="G169" t="s">
-        <v>36</v>
-      </c>
-      <c r="H169" t="s">
-        <v>22</v>
-      </c>
-      <c r="I169" t="s">
-        <v>23</v>
-      </c>
-      <c r="J169" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A170">
-        <v>100166</v>
-      </c>
-      <c r="B170" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D170" s="5">
-        <v>20050021</v>
-      </c>
-      <c r="E170" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F170">
-        <v>9000</v>
-      </c>
-      <c r="G170" t="s">
-        <v>21</v>
-      </c>
-      <c r="H170" t="s">
-        <v>38</v>
-      </c>
-      <c r="I170" t="s">
-        <v>23</v>
-      </c>
-      <c r="J170" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A171">
-        <v>100167</v>
-      </c>
-      <c r="B171" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D171" s="5">
-        <v>20050022</v>
-      </c>
-      <c r="E171" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F171">
-        <v>9000</v>
-      </c>
-      <c r="G171" t="s">
-        <v>21</v>
-      </c>
-      <c r="H171" t="s">
-        <v>38</v>
-      </c>
-      <c r="I171" t="s">
-        <v>23</v>
-      </c>
-      <c r="J171" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A172">
-        <v>100168</v>
-      </c>
-      <c r="B172" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D172" s="5">
-        <v>20050023</v>
-      </c>
-      <c r="E172" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F172">
-        <v>9000</v>
-      </c>
-      <c r="G172" t="s">
-        <v>21</v>
-      </c>
-      <c r="H172" t="s">
-        <v>38</v>
-      </c>
-      <c r="I172" t="s">
-        <v>23</v>
-      </c>
-      <c r="J172" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A173">
-        <v>100169</v>
-      </c>
-      <c r="B173" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D173" s="5">
-        <v>20050021</v>
-      </c>
-      <c r="E173" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F173">
-        <v>7000</v>
-      </c>
-      <c r="G173" t="s">
-        <v>28</v>
-      </c>
-      <c r="H173" t="s">
-        <v>38</v>
-      </c>
-      <c r="I173" t="s">
-        <v>23</v>
-      </c>
-      <c r="J173" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A174">
-        <v>100170</v>
-      </c>
-      <c r="B174" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D174" s="5">
-        <v>20050022</v>
-      </c>
-      <c r="E174" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F174">
-        <v>7000</v>
-      </c>
-      <c r="G174" t="s">
-        <v>28</v>
-      </c>
-      <c r="H174" t="s">
-        <v>38</v>
-      </c>
-      <c r="I174" t="s">
-        <v>23</v>
-      </c>
-      <c r="J174" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A175">
-        <v>100171</v>
-      </c>
-      <c r="B175" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D175" s="5">
-        <v>20050023</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F175">
-        <v>7000</v>
-      </c>
-      <c r="G175" t="s">
-        <v>28</v>
-      </c>
-      <c r="H175" t="s">
-        <v>38</v>
-      </c>
-      <c r="I175" t="s">
-        <v>23</v>
-      </c>
-      <c r="J175" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A176">
-        <v>100172</v>
-      </c>
-      <c r="B176" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D176" s="5">
-        <v>20050021</v>
-      </c>
-      <c r="E176" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F176">
-        <v>5000</v>
-      </c>
-      <c r="G176" t="s">
-        <v>31</v>
-      </c>
-      <c r="H176" t="s">
-        <v>38</v>
-      </c>
-      <c r="I176" t="s">
-        <v>23</v>
-      </c>
-      <c r="J176" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A177">
-        <v>100173</v>
-      </c>
-      <c r="B177" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D177" s="5">
-        <v>20050022</v>
-      </c>
-      <c r="E177" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F177">
-        <v>5000</v>
-      </c>
-      <c r="G177" t="s">
-        <v>31</v>
-      </c>
-      <c r="H177" t="s">
-        <v>38</v>
-      </c>
-      <c r="I177" t="s">
-        <v>23</v>
-      </c>
-      <c r="J177" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A178">
-        <v>100174</v>
-      </c>
-      <c r="B178" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D178" s="5">
-        <v>20050023</v>
-      </c>
-      <c r="E178" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F178">
-        <v>5000</v>
-      </c>
-      <c r="G178" t="s">
-        <v>31</v>
-      </c>
-      <c r="H178" t="s">
-        <v>38</v>
-      </c>
-      <c r="I178" t="s">
-        <v>23</v>
-      </c>
-      <c r="J178" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A179">
-        <v>100175</v>
-      </c>
-      <c r="B179" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D179" s="5">
-        <v>20050021</v>
-      </c>
-      <c r="E179" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F179">
-        <v>4000</v>
-      </c>
-      <c r="G179" t="s">
-        <v>34</v>
-      </c>
-      <c r="H179" t="s">
-        <v>38</v>
-      </c>
-      <c r="I179" t="s">
-        <v>23</v>
-      </c>
-      <c r="J179" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A180">
-        <v>100176</v>
-      </c>
-      <c r="B180" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D180" s="5">
-        <v>20050022</v>
-      </c>
-      <c r="E180" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F180">
-        <v>4000</v>
-      </c>
-      <c r="G180" t="s">
-        <v>34</v>
-      </c>
-      <c r="H180" t="s">
-        <v>38</v>
-      </c>
-      <c r="I180" t="s">
-        <v>23</v>
-      </c>
-      <c r="J180" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A181">
-        <v>100177</v>
-      </c>
-      <c r="B181" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D181" s="5">
-        <v>20050023</v>
-      </c>
-      <c r="E181" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F181">
-        <v>4000</v>
-      </c>
-      <c r="G181" t="s">
-        <v>34</v>
-      </c>
-      <c r="H181" t="s">
-        <v>38</v>
-      </c>
-      <c r="I181" t="s">
-        <v>23</v>
-      </c>
-      <c r="J181" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A182">
-        <v>100178</v>
-      </c>
-      <c r="B182" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D182" s="5">
-        <v>20050021</v>
-      </c>
-      <c r="E182" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F182">
-        <v>2000</v>
-      </c>
-      <c r="G182" t="s">
-        <v>36</v>
-      </c>
-      <c r="H182" t="s">
-        <v>38</v>
-      </c>
-      <c r="I182" t="s">
-        <v>23</v>
-      </c>
-      <c r="J182" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A183">
-        <v>100179</v>
-      </c>
-      <c r="B183" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D183" s="5">
-        <v>20050022</v>
-      </c>
-      <c r="E183" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F183">
-        <v>2000</v>
-      </c>
-      <c r="G183" t="s">
-        <v>36</v>
-      </c>
-      <c r="H183" t="s">
-        <v>38</v>
-      </c>
-      <c r="I183" t="s">
-        <v>23</v>
-      </c>
-      <c r="J183" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A184">
-        <v>100180</v>
-      </c>
-      <c r="B184" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D184" s="5">
-        <v>20050023</v>
-      </c>
-      <c r="E184" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F184">
-        <v>2000</v>
-      </c>
-      <c r="G184" t="s">
-        <v>36</v>
-      </c>
-      <c r="H184" t="s">
-        <v>38</v>
-      </c>
-      <c r="I184" t="s">
-        <v>23</v>
-      </c>
-      <c r="J184" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A185">
-        <v>100181</v>
-      </c>
-      <c r="B185" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D185" s="5">
-        <v>20010021</v>
-      </c>
-      <c r="E185" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F185">
-        <v>9000</v>
-      </c>
-      <c r="G185" t="s">
-        <v>21</v>
-      </c>
-      <c r="H185" t="s">
-        <v>42</v>
-      </c>
-      <c r="I185" t="s">
-        <v>23</v>
-      </c>
-      <c r="J185" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A186">
-        <v>100182</v>
-      </c>
-      <c r="B186" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D186" s="5">
-        <v>20010022</v>
-      </c>
-      <c r="E186" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F186">
-        <v>9000</v>
-      </c>
-      <c r="G186" t="s">
-        <v>21</v>
-      </c>
-      <c r="H186" t="s">
-        <v>42</v>
-      </c>
-      <c r="I186" t="s">
-        <v>23</v>
-      </c>
-      <c r="J186" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A187">
-        <v>100183</v>
-      </c>
-      <c r="B187" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D187" s="5">
-        <v>20010023</v>
-      </c>
-      <c r="E187" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F187">
-        <v>9000</v>
-      </c>
-      <c r="G187" t="s">
-        <v>21</v>
-      </c>
-      <c r="H187" t="s">
-        <v>42</v>
-      </c>
-      <c r="I187" t="s">
-        <v>23</v>
-      </c>
-      <c r="J187" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A188">
-        <v>100184</v>
-      </c>
-      <c r="B188" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D188" s="5">
-        <v>20010021</v>
-      </c>
-      <c r="E188" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F188">
-        <v>7000</v>
-      </c>
-      <c r="G188" t="s">
-        <v>28</v>
-      </c>
-      <c r="H188" t="s">
-        <v>42</v>
-      </c>
-      <c r="I188" t="s">
-        <v>23</v>
-      </c>
-      <c r="J188" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A189">
-        <v>100185</v>
-      </c>
-      <c r="B189" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D189" s="5">
-        <v>20010022</v>
-      </c>
-      <c r="E189" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F189">
-        <v>7000</v>
-      </c>
-      <c r="G189" t="s">
-        <v>28</v>
-      </c>
-      <c r="H189" t="s">
-        <v>42</v>
-      </c>
-      <c r="I189" t="s">
-        <v>23</v>
-      </c>
-      <c r="J189" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A190">
-        <v>100186</v>
-      </c>
-      <c r="B190" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D190" s="5">
-        <v>20010023</v>
-      </c>
-      <c r="E190" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F190">
-        <v>7000</v>
-      </c>
-      <c r="G190" t="s">
-        <v>28</v>
-      </c>
-      <c r="H190" t="s">
-        <v>42</v>
-      </c>
-      <c r="I190" t="s">
-        <v>23</v>
-      </c>
-      <c r="J190" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A191">
-        <v>100187</v>
-      </c>
-      <c r="B191" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D191" s="5">
-        <v>20010021</v>
-      </c>
-      <c r="E191" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F191">
-        <v>5000</v>
-      </c>
-      <c r="G191" t="s">
-        <v>31</v>
-      </c>
-      <c r="H191" t="s">
-        <v>42</v>
-      </c>
-      <c r="I191" t="s">
-        <v>23</v>
-      </c>
-      <c r="J191" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A192">
-        <v>100188</v>
-      </c>
-      <c r="B192" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D192" s="5">
-        <v>20010022</v>
-      </c>
-      <c r="E192" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F192">
-        <v>5000</v>
-      </c>
-      <c r="G192" t="s">
-        <v>31</v>
-      </c>
-      <c r="H192" t="s">
-        <v>42</v>
-      </c>
-      <c r="I192" t="s">
-        <v>23</v>
-      </c>
-      <c r="J192" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A193">
-        <v>100189</v>
-      </c>
-      <c r="B193" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D193" s="5">
-        <v>20010023</v>
-      </c>
-      <c r="E193" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F193">
-        <v>5000</v>
-      </c>
-      <c r="G193" t="s">
-        <v>31</v>
-      </c>
-      <c r="H193" t="s">
-        <v>42</v>
-      </c>
-      <c r="I193" t="s">
-        <v>23</v>
-      </c>
-      <c r="J193" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A194">
-        <v>100190</v>
-      </c>
-      <c r="B194" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D194" s="5">
-        <v>20010021</v>
-      </c>
-      <c r="E194" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F194">
-        <v>4000</v>
-      </c>
-      <c r="G194" t="s">
-        <v>34</v>
-      </c>
-      <c r="H194" t="s">
-        <v>42</v>
-      </c>
-      <c r="I194" t="s">
-        <v>23</v>
-      </c>
-      <c r="J194" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A195">
-        <v>100191</v>
-      </c>
-      <c r="B195" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D195" s="5">
-        <v>20010022</v>
-      </c>
-      <c r="E195" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F195">
-        <v>4000</v>
-      </c>
-      <c r="G195" t="s">
-        <v>34</v>
-      </c>
-      <c r="H195" t="s">
-        <v>42</v>
-      </c>
-      <c r="I195" t="s">
-        <v>23</v>
-      </c>
-      <c r="J195" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A196">
-        <v>100192</v>
-      </c>
-      <c r="B196" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D196" s="5">
-        <v>20010023</v>
-      </c>
-      <c r="E196" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F196">
-        <v>4000</v>
-      </c>
-      <c r="G196" t="s">
-        <v>34</v>
-      </c>
-      <c r="H196" t="s">
-        <v>42</v>
-      </c>
-      <c r="I196" t="s">
-        <v>23</v>
-      </c>
-      <c r="J196" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A197">
-        <v>100193</v>
-      </c>
-      <c r="B197" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D197" s="5">
-        <v>20010021</v>
-      </c>
-      <c r="E197" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F197">
-        <v>2000</v>
-      </c>
-      <c r="G197" t="s">
-        <v>36</v>
-      </c>
-      <c r="H197" t="s">
-        <v>42</v>
-      </c>
-      <c r="I197" t="s">
-        <v>23</v>
-      </c>
-      <c r="J197" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A198">
-        <v>100194</v>
-      </c>
-      <c r="B198" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D198" s="5">
-        <v>20010022</v>
-      </c>
-      <c r="E198" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F198">
-        <v>2000</v>
-      </c>
-      <c r="G198" t="s">
-        <v>36</v>
-      </c>
-      <c r="H198" t="s">
-        <v>42</v>
-      </c>
-      <c r="I198" t="s">
-        <v>23</v>
-      </c>
-      <c r="J198" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A199">
-        <v>100195</v>
-      </c>
-      <c r="B199" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D199" s="5">
-        <v>20010023</v>
-      </c>
-      <c r="E199" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F199">
-        <v>2000</v>
-      </c>
-      <c r="G199" t="s">
-        <v>36</v>
-      </c>
-      <c r="H199" t="s">
-        <v>42</v>
-      </c>
-      <c r="I199" t="s">
-        <v>23</v>
-      </c>
-      <c r="J199" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A200">
-        <v>100196</v>
-      </c>
-      <c r="B200" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D200" s="5">
-        <v>20030021</v>
-      </c>
-      <c r="E200" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F200">
-        <v>9000</v>
-      </c>
-      <c r="G200" t="s">
-        <v>21</v>
-      </c>
-      <c r="H200" t="s">
-        <v>46</v>
-      </c>
-      <c r="I200" t="s">
-        <v>23</v>
-      </c>
-      <c r="J200" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A201">
-        <v>100197</v>
-      </c>
-      <c r="B201" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D201" s="5">
-        <v>20030022</v>
-      </c>
-      <c r="E201" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F201">
-        <v>9000</v>
-      </c>
-      <c r="G201" t="s">
-        <v>21</v>
-      </c>
-      <c r="H201" t="s">
-        <v>46</v>
-      </c>
-      <c r="I201" t="s">
-        <v>23</v>
-      </c>
-      <c r="J201" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A202">
-        <v>100198</v>
-      </c>
-      <c r="B202" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D202" s="5">
-        <v>20030023</v>
-      </c>
-      <c r="E202" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F202">
-        <v>9000</v>
-      </c>
-      <c r="G202" t="s">
-        <v>21</v>
-      </c>
-      <c r="H202" t="s">
-        <v>46</v>
-      </c>
-      <c r="I202" t="s">
-        <v>23</v>
-      </c>
-      <c r="J202" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A203">
-        <v>100199</v>
-      </c>
-      <c r="B203" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D203" s="5">
-        <v>20030021</v>
-      </c>
-      <c r="E203" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F203">
-        <v>7000</v>
-      </c>
-      <c r="G203" t="s">
-        <v>28</v>
-      </c>
-      <c r="H203" t="s">
-        <v>46</v>
-      </c>
-      <c r="I203" t="s">
-        <v>23</v>
-      </c>
-      <c r="J203" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A204">
-        <v>100200</v>
-      </c>
-      <c r="B204" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D204" s="5">
-        <v>20030022</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F204">
-        <v>7000</v>
-      </c>
-      <c r="G204" t="s">
-        <v>28</v>
-      </c>
-      <c r="H204" t="s">
-        <v>46</v>
-      </c>
-      <c r="I204" t="s">
-        <v>23</v>
-      </c>
-      <c r="J204" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A205">
-        <v>100201</v>
-      </c>
-      <c r="B205" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D205" s="5">
-        <v>20030023</v>
-      </c>
-      <c r="E205" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F205">
-        <v>7000</v>
-      </c>
-      <c r="G205" t="s">
-        <v>28</v>
-      </c>
-      <c r="H205" t="s">
-        <v>46</v>
-      </c>
-      <c r="I205" t="s">
-        <v>23</v>
-      </c>
-      <c r="J205" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A206">
-        <v>100202</v>
-      </c>
-      <c r="B206" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D206" s="5">
-        <v>20030021</v>
-      </c>
-      <c r="E206" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F206">
-        <v>5000</v>
-      </c>
-      <c r="G206" t="s">
-        <v>31</v>
-      </c>
-      <c r="H206" t="s">
-        <v>46</v>
-      </c>
-      <c r="I206" t="s">
-        <v>23</v>
-      </c>
-      <c r="J206" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A207">
-        <v>100203</v>
-      </c>
-      <c r="B207" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D207" s="5">
-        <v>20030022</v>
-      </c>
-      <c r="E207" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F207">
-        <v>5000</v>
-      </c>
-      <c r="G207" t="s">
-        <v>31</v>
-      </c>
-      <c r="H207" t="s">
-        <v>46</v>
-      </c>
-      <c r="I207" t="s">
-        <v>23</v>
-      </c>
-      <c r="J207" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A208">
-        <v>100204</v>
-      </c>
-      <c r="B208" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D208" s="5">
-        <v>20030023</v>
-      </c>
-      <c r="E208" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F208">
-        <v>5000</v>
-      </c>
-      <c r="G208" t="s">
-        <v>31</v>
-      </c>
-      <c r="H208" t="s">
-        <v>46</v>
-      </c>
-      <c r="I208" t="s">
-        <v>23</v>
-      </c>
-      <c r="J208" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A209">
-        <v>100205</v>
-      </c>
-      <c r="B209" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D209" s="5">
-        <v>20030021</v>
-      </c>
-      <c r="E209" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F209">
-        <v>4000</v>
-      </c>
-      <c r="G209" t="s">
-        <v>34</v>
-      </c>
-      <c r="H209" t="s">
-        <v>46</v>
-      </c>
-      <c r="I209" t="s">
-        <v>23</v>
-      </c>
-      <c r="J209" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A210">
-        <v>100206</v>
-      </c>
-      <c r="B210" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D210" s="5">
-        <v>20030022</v>
-      </c>
-      <c r="E210" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F210">
-        <v>4000</v>
-      </c>
-      <c r="G210" t="s">
-        <v>34</v>
-      </c>
-      <c r="H210" t="s">
-        <v>46</v>
-      </c>
-      <c r="I210" t="s">
-        <v>23</v>
-      </c>
-      <c r="J210" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A211">
-        <v>100207</v>
-      </c>
-      <c r="B211" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D211" s="5">
-        <v>20030023</v>
-      </c>
-      <c r="E211" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F211">
-        <v>4000</v>
-      </c>
-      <c r="G211" t="s">
-        <v>34</v>
-      </c>
-      <c r="H211" t="s">
-        <v>46</v>
-      </c>
-      <c r="I211" t="s">
-        <v>23</v>
-      </c>
-      <c r="J211" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A212">
-        <v>100208</v>
-      </c>
-      <c r="B212" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D212" s="5">
-        <v>20030021</v>
-      </c>
-      <c r="E212" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F212">
-        <v>2000</v>
-      </c>
-      <c r="G212" t="s">
-        <v>36</v>
-      </c>
-      <c r="H212" t="s">
-        <v>46</v>
-      </c>
-      <c r="I212" t="s">
-        <v>23</v>
-      </c>
-      <c r="J212" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A213">
-        <v>100209</v>
-      </c>
-      <c r="B213" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C213" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D213" s="5">
-        <v>20030022</v>
-      </c>
-      <c r="E213" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F213">
-        <v>2000</v>
-      </c>
-      <c r="G213" t="s">
-        <v>36</v>
-      </c>
-      <c r="H213" t="s">
-        <v>46</v>
-      </c>
-      <c r="I213" t="s">
-        <v>23</v>
-      </c>
-      <c r="J213" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A214">
-        <v>100210</v>
-      </c>
-      <c r="B214" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D214" s="5">
-        <v>20030023</v>
-      </c>
-      <c r="E214" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F214">
-        <v>2000</v>
-      </c>
-      <c r="G214" t="s">
-        <v>36</v>
-      </c>
-      <c r="H214" t="s">
-        <v>46</v>
-      </c>
-      <c r="I214" t="s">
-        <v>23</v>
-      </c>
-      <c r="J214" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A215">
-        <v>100211</v>
-      </c>
-      <c r="B215" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D215" s="5">
-        <v>20010121</v>
-      </c>
-      <c r="E215" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F215">
-        <v>9000</v>
-      </c>
-      <c r="G215" t="s">
-        <v>21</v>
-      </c>
-      <c r="H215" t="s">
-        <v>50</v>
-      </c>
-      <c r="I215" t="s">
-        <v>23</v>
-      </c>
-      <c r="J215" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A216">
-        <v>100212</v>
-      </c>
-      <c r="B216" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D216" s="5">
-        <v>20010122</v>
-      </c>
-      <c r="E216" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F216">
-        <v>9000</v>
-      </c>
-      <c r="G216" t="s">
-        <v>21</v>
-      </c>
-      <c r="H216" t="s">
-        <v>50</v>
-      </c>
-      <c r="I216" t="s">
-        <v>23</v>
-      </c>
-      <c r="J216" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A217">
-        <v>100213</v>
-      </c>
-      <c r="B217" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D217" s="5">
-        <v>20010123</v>
-      </c>
-      <c r="E217" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F217">
-        <v>9000</v>
-      </c>
-      <c r="G217" t="s">
-        <v>21</v>
-      </c>
-      <c r="H217" t="s">
-        <v>50</v>
-      </c>
-      <c r="I217" t="s">
-        <v>23</v>
-      </c>
-      <c r="J217" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A218">
-        <v>100214</v>
-      </c>
-      <c r="B218" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D218" s="5">
-        <v>20010121</v>
-      </c>
-      <c r="E218" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F218">
-        <v>7000</v>
-      </c>
-      <c r="G218" t="s">
-        <v>28</v>
-      </c>
-      <c r="H218" t="s">
-        <v>50</v>
-      </c>
-      <c r="I218" t="s">
-        <v>23</v>
-      </c>
-      <c r="J218" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A219">
-        <v>100215</v>
-      </c>
-      <c r="B219" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D219" s="5">
-        <v>20010122</v>
-      </c>
-      <c r="E219" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F219">
-        <v>7000</v>
-      </c>
-      <c r="G219" t="s">
-        <v>28</v>
-      </c>
-      <c r="H219" t="s">
-        <v>50</v>
-      </c>
-      <c r="I219" t="s">
-        <v>23</v>
-      </c>
-      <c r="J219" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A220">
-        <v>100216</v>
-      </c>
-      <c r="B220" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D220" s="5">
-        <v>20010123</v>
-      </c>
-      <c r="E220" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F220">
-        <v>7000</v>
-      </c>
-      <c r="G220" t="s">
-        <v>28</v>
-      </c>
-      <c r="H220" t="s">
-        <v>50</v>
-      </c>
-      <c r="I220" t="s">
-        <v>23</v>
-      </c>
-      <c r="J220" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A221">
-        <v>100217</v>
-      </c>
-      <c r="B221" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D221" s="5">
-        <v>20010121</v>
-      </c>
-      <c r="E221" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F221">
-        <v>5000</v>
-      </c>
-      <c r="G221" t="s">
-        <v>31</v>
-      </c>
-      <c r="H221" t="s">
-        <v>50</v>
-      </c>
-      <c r="I221" t="s">
-        <v>23</v>
-      </c>
-      <c r="J221" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A222">
-        <v>100218</v>
-      </c>
-      <c r="B222" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D222" s="5">
-        <v>20010122</v>
-      </c>
-      <c r="E222" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F222">
-        <v>5000</v>
-      </c>
-      <c r="G222" t="s">
-        <v>31</v>
-      </c>
-      <c r="H222" t="s">
-        <v>50</v>
-      </c>
-      <c r="I222" t="s">
-        <v>23</v>
-      </c>
-      <c r="J222" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A223">
-        <v>100219</v>
-      </c>
-      <c r="B223" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D223" s="5">
-        <v>20010123</v>
-      </c>
-      <c r="E223" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F223">
-        <v>5000</v>
-      </c>
-      <c r="G223" t="s">
-        <v>31</v>
-      </c>
-      <c r="H223" t="s">
-        <v>50</v>
-      </c>
-      <c r="I223" t="s">
-        <v>23</v>
-      </c>
-      <c r="J223" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A224">
-        <v>100220</v>
-      </c>
-      <c r="B224" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D224" s="5">
-        <v>20010121</v>
-      </c>
-      <c r="E224" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F224">
-        <v>4000</v>
-      </c>
-      <c r="G224" t="s">
-        <v>34</v>
-      </c>
-      <c r="H224" t="s">
-        <v>50</v>
-      </c>
-      <c r="I224" t="s">
-        <v>23</v>
-      </c>
-      <c r="J224" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A225">
-        <v>100221</v>
-      </c>
-      <c r="B225" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D225" s="5">
-        <v>20010122</v>
-      </c>
-      <c r="E225" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F225">
-        <v>4000</v>
-      </c>
-      <c r="G225" t="s">
-        <v>34</v>
-      </c>
-      <c r="H225" t="s">
-        <v>50</v>
-      </c>
-      <c r="I225" t="s">
-        <v>23</v>
-      </c>
-      <c r="J225" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A226">
-        <v>100222</v>
-      </c>
-      <c r="B226" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D226" s="5">
-        <v>20010123</v>
-      </c>
-      <c r="E226" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F226">
-        <v>4000</v>
-      </c>
-      <c r="G226" t="s">
-        <v>34</v>
-      </c>
-      <c r="H226" t="s">
-        <v>50</v>
-      </c>
-      <c r="I226" t="s">
-        <v>23</v>
-      </c>
-      <c r="J226" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A227">
-        <v>100223</v>
-      </c>
-      <c r="B227" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D227" s="5">
-        <v>20010121</v>
-      </c>
-      <c r="E227" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F227">
-        <v>2000</v>
-      </c>
-      <c r="G227" t="s">
-        <v>36</v>
-      </c>
-      <c r="H227" t="s">
-        <v>50</v>
-      </c>
-      <c r="I227" t="s">
-        <v>23</v>
-      </c>
-      <c r="J227" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A228">
-        <v>100224</v>
-      </c>
-      <c r="B228" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D228" s="5">
-        <v>20010122</v>
-      </c>
-      <c r="E228" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F228">
-        <v>2000</v>
-      </c>
-      <c r="G228" t="s">
-        <v>36</v>
-      </c>
-      <c r="H228" t="s">
-        <v>50</v>
-      </c>
-      <c r="I228" t="s">
-        <v>23</v>
-      </c>
-      <c r="J228" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A229">
-        <v>100225</v>
-      </c>
-      <c r="B229" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D229" s="5">
-        <v>20010123</v>
-      </c>
-      <c r="E229" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F229">
-        <v>2000</v>
-      </c>
-      <c r="G229" t="s">
-        <v>36</v>
-      </c>
-      <c r="H229" t="s">
-        <v>50</v>
-      </c>
-      <c r="I229" t="s">
-        <v>23</v>
-      </c>
-      <c r="J229" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A230">
-        <v>100226</v>
-      </c>
-      <c r="B230" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D230" s="5">
-        <v>20060021</v>
-      </c>
-      <c r="E230" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F230">
-        <v>9000</v>
-      </c>
-      <c r="G230" t="s">
-        <v>21</v>
-      </c>
-      <c r="H230" t="s">
-        <v>54</v>
-      </c>
-      <c r="I230" t="s">
-        <v>23</v>
-      </c>
-      <c r="J230" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A231">
-        <v>100227</v>
-      </c>
-      <c r="B231" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D231" s="5">
-        <v>20060022</v>
-      </c>
-      <c r="E231" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F231">
-        <v>9000</v>
-      </c>
-      <c r="G231" t="s">
-        <v>21</v>
-      </c>
-      <c r="H231" t="s">
-        <v>54</v>
-      </c>
-      <c r="I231" t="s">
-        <v>23</v>
-      </c>
-      <c r="J231" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A232">
-        <v>100228</v>
-      </c>
-      <c r="B232" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D232" s="5">
-        <v>20060023</v>
-      </c>
-      <c r="E232" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F232">
-        <v>9000</v>
-      </c>
-      <c r="G232" t="s">
-        <v>21</v>
-      </c>
-      <c r="H232" t="s">
-        <v>54</v>
-      </c>
-      <c r="I232" t="s">
-        <v>23</v>
-      </c>
-      <c r="J232" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A233">
-        <v>100229</v>
-      </c>
-      <c r="B233" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C233" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D233" s="5">
-        <v>20060021</v>
-      </c>
-      <c r="E233" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F233">
-        <v>7000</v>
-      </c>
-      <c r="G233" t="s">
-        <v>28</v>
-      </c>
-      <c r="H233" t="s">
-        <v>54</v>
-      </c>
-      <c r="I233" t="s">
-        <v>23</v>
-      </c>
-      <c r="J233" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A234">
-        <v>100230</v>
-      </c>
-      <c r="B234" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D234" s="5">
-        <v>20060022</v>
-      </c>
-      <c r="E234" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F234">
-        <v>7000</v>
-      </c>
-      <c r="G234" t="s">
-        <v>28</v>
-      </c>
-      <c r="H234" t="s">
-        <v>54</v>
-      </c>
-      <c r="I234" t="s">
-        <v>23</v>
-      </c>
-      <c r="J234" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A235">
-        <v>100231</v>
-      </c>
-      <c r="B235" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C235" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D235" s="5">
-        <v>20060023</v>
-      </c>
-      <c r="E235" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F235">
-        <v>7000</v>
-      </c>
-      <c r="G235" t="s">
-        <v>28</v>
-      </c>
-      <c r="H235" t="s">
-        <v>54</v>
-      </c>
-      <c r="I235" t="s">
-        <v>23</v>
-      </c>
-      <c r="J235" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A236">
-        <v>100232</v>
-      </c>
-      <c r="B236" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D236" s="5">
-        <v>20060021</v>
-      </c>
-      <c r="E236" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F236">
-        <v>5000</v>
-      </c>
-      <c r="G236" t="s">
-        <v>31</v>
-      </c>
-      <c r="H236" t="s">
-        <v>54</v>
-      </c>
-      <c r="I236" t="s">
-        <v>23</v>
-      </c>
-      <c r="J236" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A237">
-        <v>100233</v>
-      </c>
-      <c r="B237" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D237" s="5">
-        <v>20060022</v>
-      </c>
-      <c r="E237" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F237">
-        <v>5000</v>
-      </c>
-      <c r="G237" t="s">
-        <v>31</v>
-      </c>
-      <c r="H237" t="s">
-        <v>54</v>
-      </c>
-      <c r="I237" t="s">
-        <v>23</v>
-      </c>
-      <c r="J237" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A238">
-        <v>100234</v>
-      </c>
-      <c r="B238" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D238" s="5">
-        <v>20060023</v>
-      </c>
-      <c r="E238" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F238">
-        <v>5000</v>
-      </c>
-      <c r="G238" t="s">
-        <v>31</v>
-      </c>
-      <c r="H238" t="s">
-        <v>54</v>
-      </c>
-      <c r="I238" t="s">
-        <v>23</v>
-      </c>
-      <c r="J238" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A239">
-        <v>100235</v>
-      </c>
-      <c r="B239" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D239" s="5">
-        <v>20060021</v>
-      </c>
-      <c r="E239" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F239">
-        <v>4000</v>
-      </c>
-      <c r="G239" t="s">
-        <v>34</v>
-      </c>
-      <c r="H239" t="s">
-        <v>54</v>
-      </c>
-      <c r="I239" t="s">
-        <v>23</v>
-      </c>
-      <c r="J239" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A240">
-        <v>100236</v>
-      </c>
-      <c r="B240" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D240" s="5">
-        <v>20060022</v>
-      </c>
-      <c r="E240" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F240">
-        <v>4000</v>
-      </c>
-      <c r="G240" t="s">
-        <v>34</v>
-      </c>
-      <c r="H240" t="s">
-        <v>54</v>
-      </c>
-      <c r="I240" t="s">
-        <v>23</v>
-      </c>
-      <c r="J240" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A241">
-        <v>100237</v>
-      </c>
-      <c r="B241" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C241" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D241" s="5">
-        <v>20060023</v>
-      </c>
-      <c r="E241" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F241">
-        <v>4000</v>
-      </c>
-      <c r="G241" t="s">
-        <v>34</v>
-      </c>
-      <c r="H241" t="s">
-        <v>54</v>
-      </c>
-      <c r="I241" t="s">
-        <v>23</v>
-      </c>
-      <c r="J241" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A242">
-        <v>100238</v>
-      </c>
-      <c r="B242" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D242" s="5">
-        <v>20060021</v>
-      </c>
-      <c r="E242" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F242">
-        <v>2000</v>
-      </c>
-      <c r="G242" t="s">
-        <v>36</v>
-      </c>
-      <c r="H242" t="s">
-        <v>54</v>
-      </c>
-      <c r="I242" t="s">
-        <v>23</v>
-      </c>
-      <c r="J242" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A243">
-        <v>100239</v>
-      </c>
-      <c r="B243" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C243" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D243" s="5">
-        <v>20060022</v>
-      </c>
-      <c r="E243" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F243">
-        <v>2000</v>
-      </c>
-      <c r="G243" t="s">
-        <v>36</v>
-      </c>
-      <c r="H243" t="s">
-        <v>54</v>
-      </c>
-      <c r="I243" t="s">
-        <v>23</v>
-      </c>
-      <c r="J243" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A244">
-        <v>100240</v>
-      </c>
-      <c r="B244" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C244" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D244" s="5">
-        <v>20060023</v>
-      </c>
-      <c r="E244" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F244">
-        <v>2000</v>
-      </c>
-      <c r="G244" t="s">
-        <v>36</v>
-      </c>
-      <c r="H244" t="s">
-        <v>54</v>
-      </c>
-      <c r="I244" t="s">
-        <v>23</v>
-      </c>
-      <c r="J244" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A245">
-        <v>100241</v>
-      </c>
-      <c r="B245" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C245" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D245" s="5">
-        <v>20070021</v>
-      </c>
-      <c r="E245" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F245">
-        <v>9000</v>
-      </c>
-      <c r="G245" t="s">
-        <v>21</v>
-      </c>
-      <c r="H245" t="s">
-        <v>58</v>
-      </c>
-      <c r="I245" t="s">
-        <v>23</v>
-      </c>
-      <c r="J245" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A246">
-        <v>100242</v>
-      </c>
-      <c r="B246" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D246" s="5">
-        <v>20070022</v>
-      </c>
-      <c r="E246" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F246">
-        <v>9000</v>
-      </c>
-      <c r="G246" t="s">
-        <v>21</v>
-      </c>
-      <c r="H246" t="s">
-        <v>58</v>
-      </c>
-      <c r="I246" t="s">
-        <v>23</v>
-      </c>
-      <c r="J246" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A247">
-        <v>100243</v>
-      </c>
-      <c r="B247" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C247" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D247" s="5">
-        <v>20070023</v>
-      </c>
-      <c r="E247" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F247">
-        <v>9000</v>
-      </c>
-      <c r="G247" t="s">
-        <v>21</v>
-      </c>
-      <c r="H247" t="s">
-        <v>58</v>
-      </c>
-      <c r="I247" t="s">
-        <v>23</v>
-      </c>
-      <c r="J247" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A248">
-        <v>100244</v>
-      </c>
-      <c r="B248" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D248" s="5">
-        <v>20070021</v>
-      </c>
-      <c r="E248" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F248">
-        <v>7000</v>
-      </c>
-      <c r="G248" t="s">
-        <v>28</v>
-      </c>
-      <c r="H248" t="s">
-        <v>58</v>
-      </c>
-      <c r="I248" t="s">
-        <v>23</v>
-      </c>
-      <c r="J248" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A249">
-        <v>100245</v>
-      </c>
-      <c r="B249" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C249" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D249" s="5">
-        <v>20070022</v>
-      </c>
-      <c r="E249" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F249">
-        <v>7000</v>
-      </c>
-      <c r="G249" t="s">
-        <v>28</v>
-      </c>
-      <c r="H249" t="s">
-        <v>58</v>
-      </c>
-      <c r="I249" t="s">
-        <v>23</v>
-      </c>
-      <c r="J249" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A250">
-        <v>100246</v>
-      </c>
-      <c r="B250" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D250" s="5">
-        <v>20070023</v>
-      </c>
-      <c r="E250" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F250">
-        <v>7000</v>
-      </c>
-      <c r="G250" t="s">
-        <v>28</v>
-      </c>
-      <c r="H250" t="s">
-        <v>58</v>
-      </c>
-      <c r="I250" t="s">
-        <v>23</v>
-      </c>
-      <c r="J250" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A251">
-        <v>100247</v>
-      </c>
-      <c r="B251" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D251" s="5">
-        <v>20070021</v>
-      </c>
-      <c r="E251" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F251">
-        <v>5000</v>
-      </c>
-      <c r="G251" t="s">
-        <v>31</v>
-      </c>
-      <c r="H251" t="s">
-        <v>58</v>
-      </c>
-      <c r="I251" t="s">
-        <v>23</v>
-      </c>
-      <c r="J251" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A252">
-        <v>100248</v>
-      </c>
-      <c r="B252" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C252" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D252" s="5">
-        <v>20070022</v>
-      </c>
-      <c r="E252" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F252">
-        <v>5000</v>
-      </c>
-      <c r="G252" t="s">
-        <v>31</v>
-      </c>
-      <c r="H252" t="s">
-        <v>58</v>
-      </c>
-      <c r="I252" t="s">
-        <v>23</v>
-      </c>
-      <c r="J252" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A253">
-        <v>100249</v>
-      </c>
-      <c r="B253" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C253" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D253" s="5">
-        <v>20070023</v>
-      </c>
-      <c r="E253" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F253">
-        <v>5000</v>
-      </c>
-      <c r="G253" t="s">
-        <v>31</v>
-      </c>
-      <c r="H253" t="s">
-        <v>58</v>
-      </c>
-      <c r="I253" t="s">
-        <v>23</v>
-      </c>
-      <c r="J253" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A254">
-        <v>100250</v>
-      </c>
-      <c r="B254" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C254" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D254" s="5">
-        <v>20070021</v>
-      </c>
-      <c r="E254" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F254">
-        <v>4000</v>
-      </c>
-      <c r="G254" t="s">
-        <v>34</v>
-      </c>
-      <c r="H254" t="s">
-        <v>58</v>
-      </c>
-      <c r="I254" t="s">
-        <v>23</v>
-      </c>
-      <c r="J254" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A255">
-        <v>100251</v>
-      </c>
-      <c r="B255" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C255" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D255" s="5">
-        <v>20070022</v>
-      </c>
-      <c r="E255" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F255">
-        <v>4000</v>
-      </c>
-      <c r="G255" t="s">
-        <v>34</v>
-      </c>
-      <c r="H255" t="s">
-        <v>58</v>
-      </c>
-      <c r="I255" t="s">
-        <v>23</v>
-      </c>
-      <c r="J255" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A256">
-        <v>100252</v>
-      </c>
-      <c r="B256" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D256" s="5">
-        <v>20070023</v>
-      </c>
-      <c r="E256" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F256">
-        <v>4000</v>
-      </c>
-      <c r="G256" t="s">
-        <v>34</v>
-      </c>
-      <c r="H256" t="s">
-        <v>58</v>
-      </c>
-      <c r="I256" t="s">
-        <v>23</v>
-      </c>
-      <c r="J256" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A257">
-        <v>100253</v>
-      </c>
-      <c r="B257" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C257" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D257" s="5">
-        <v>20070021</v>
-      </c>
-      <c r="E257" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F257">
-        <v>2000</v>
-      </c>
-      <c r="G257" t="s">
-        <v>36</v>
-      </c>
-      <c r="H257" t="s">
-        <v>58</v>
-      </c>
-      <c r="I257" t="s">
-        <v>23</v>
-      </c>
-      <c r="J257" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A258">
-        <v>100254</v>
-      </c>
-      <c r="B258" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D258" s="5">
-        <v>20070022</v>
-      </c>
-      <c r="E258" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F258">
-        <v>2000</v>
-      </c>
-      <c r="G258" t="s">
-        <v>36</v>
-      </c>
-      <c r="H258" t="s">
-        <v>58</v>
-      </c>
-      <c r="I258" t="s">
-        <v>23</v>
-      </c>
-      <c r="J258" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A259">
-        <v>100255</v>
-      </c>
-      <c r="B259" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C259" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D259" s="5">
-        <v>20070023</v>
-      </c>
-      <c r="E259" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F259">
-        <v>2000</v>
-      </c>
-      <c r="G259" t="s">
-        <v>36</v>
-      </c>
-      <c r="H259" t="s">
-        <v>58</v>
-      </c>
-      <c r="I259" t="s">
-        <v>23</v>
-      </c>
-      <c r="J259" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A260">
-        <v>100256</v>
-      </c>
-      <c r="B260" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D260" s="5">
-        <v>20080021</v>
-      </c>
-      <c r="E260" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F260">
-        <v>9000</v>
-      </c>
-      <c r="G260" t="s">
-        <v>21</v>
-      </c>
-      <c r="H260" t="s">
-        <v>62</v>
-      </c>
-      <c r="I260" t="s">
-        <v>23</v>
-      </c>
-      <c r="J260" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A261">
-        <v>100257</v>
-      </c>
-      <c r="B261" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D261" s="5">
-        <v>20080022</v>
-      </c>
-      <c r="E261" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F261">
-        <v>9000</v>
-      </c>
-      <c r="G261" t="s">
-        <v>21</v>
-      </c>
-      <c r="H261" t="s">
-        <v>62</v>
-      </c>
-      <c r="I261" t="s">
-        <v>23</v>
-      </c>
-      <c r="J261" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A262">
-        <v>100258</v>
-      </c>
-      <c r="B262" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D262" s="5">
-        <v>20080023</v>
-      </c>
-      <c r="E262" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F262">
-        <v>9000</v>
-      </c>
-      <c r="G262" t="s">
-        <v>21</v>
-      </c>
-      <c r="H262" t="s">
-        <v>62</v>
-      </c>
-      <c r="I262" t="s">
-        <v>23</v>
-      </c>
-      <c r="J262" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A263">
-        <v>100259</v>
-      </c>
-      <c r="B263" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C263" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D263" s="5">
-        <v>20080021</v>
-      </c>
-      <c r="E263" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F263">
-        <v>7000</v>
-      </c>
-      <c r="G263" t="s">
-        <v>28</v>
-      </c>
-      <c r="H263" t="s">
-        <v>62</v>
-      </c>
-      <c r="I263" t="s">
-        <v>23</v>
-      </c>
-      <c r="J263" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A264">
-        <v>100260</v>
-      </c>
-      <c r="B264" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D264" s="5">
-        <v>20080022</v>
-      </c>
-      <c r="E264" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F264">
-        <v>7000</v>
-      </c>
-      <c r="G264" t="s">
-        <v>28</v>
-      </c>
-      <c r="H264" t="s">
-        <v>62</v>
-      </c>
-      <c r="I264" t="s">
-        <v>23</v>
-      </c>
-      <c r="J264" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A265">
-        <v>100261</v>
-      </c>
-      <c r="B265" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C265" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D265" s="5">
-        <v>20080023</v>
-      </c>
-      <c r="E265" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F265">
-        <v>7000</v>
-      </c>
-      <c r="G265" t="s">
-        <v>28</v>
-      </c>
-      <c r="H265" t="s">
-        <v>62</v>
-      </c>
-      <c r="I265" t="s">
-        <v>23</v>
-      </c>
-      <c r="J265" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A266">
-        <v>100262</v>
-      </c>
-      <c r="B266" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D266" s="5">
-        <v>20080021</v>
-      </c>
-      <c r="E266" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F266">
-        <v>5000</v>
-      </c>
-      <c r="G266" t="s">
-        <v>31</v>
-      </c>
-      <c r="H266" t="s">
-        <v>62</v>
-      </c>
-      <c r="I266" t="s">
-        <v>23</v>
-      </c>
-      <c r="J266" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A267">
-        <v>100263</v>
-      </c>
-      <c r="B267" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D267" s="5">
-        <v>20080022</v>
-      </c>
-      <c r="E267" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F267">
-        <v>5000</v>
-      </c>
-      <c r="G267" t="s">
-        <v>31</v>
-      </c>
-      <c r="H267" t="s">
-        <v>62</v>
-      </c>
-      <c r="I267" t="s">
-        <v>23</v>
-      </c>
-      <c r="J267" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A268">
-        <v>100264</v>
-      </c>
-      <c r="B268" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D268" s="5">
-        <v>20080023</v>
-      </c>
-      <c r="E268" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F268">
-        <v>5000</v>
-      </c>
-      <c r="G268" t="s">
-        <v>31</v>
-      </c>
-      <c r="H268" t="s">
-        <v>62</v>
-      </c>
-      <c r="I268" t="s">
-        <v>23</v>
-      </c>
-      <c r="J268" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A269">
-        <v>100265</v>
-      </c>
-      <c r="B269" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D269" s="5">
-        <v>20080021</v>
-      </c>
-      <c r="E269" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F269">
-        <v>4000</v>
-      </c>
-      <c r="G269" t="s">
-        <v>34</v>
-      </c>
-      <c r="H269" t="s">
-        <v>62</v>
-      </c>
-      <c r="I269" t="s">
-        <v>23</v>
-      </c>
-      <c r="J269" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A270">
-        <v>100266</v>
-      </c>
-      <c r="B270" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D270" s="5">
-        <v>20080022</v>
-      </c>
-      <c r="E270" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F270">
-        <v>4000</v>
-      </c>
-      <c r="G270" t="s">
-        <v>34</v>
-      </c>
-      <c r="H270" t="s">
-        <v>62</v>
-      </c>
-      <c r="I270" t="s">
-        <v>23</v>
-      </c>
-      <c r="J270" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A271">
-        <v>100267</v>
-      </c>
-      <c r="B271" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C271" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D271" s="5">
-        <v>20080023</v>
-      </c>
-      <c r="E271" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F271">
-        <v>4000</v>
-      </c>
-      <c r="G271" t="s">
-        <v>34</v>
-      </c>
-      <c r="H271" t="s">
-        <v>62</v>
-      </c>
-      <c r="I271" t="s">
-        <v>23</v>
-      </c>
-      <c r="J271" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A272">
-        <v>100268</v>
-      </c>
-      <c r="B272" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D272" s="5">
-        <v>20080021</v>
-      </c>
-      <c r="E272" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F272">
-        <v>2000</v>
-      </c>
-      <c r="G272" t="s">
-        <v>36</v>
-      </c>
-      <c r="H272" t="s">
-        <v>62</v>
-      </c>
-      <c r="I272" t="s">
-        <v>23</v>
-      </c>
-      <c r="J272" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A273">
-        <v>100269</v>
-      </c>
-      <c r="B273" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D273" s="5">
-        <v>20080022</v>
-      </c>
-      <c r="E273" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F273">
-        <v>2000</v>
-      </c>
-      <c r="G273" t="s">
-        <v>36</v>
-      </c>
-      <c r="H273" t="s">
-        <v>62</v>
-      </c>
-      <c r="I273" t="s">
-        <v>23</v>
-      </c>
-      <c r="J273" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A274">
-        <v>100270</v>
-      </c>
-      <c r="B274" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D274" s="5">
-        <v>20080023</v>
-      </c>
-      <c r="E274" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F274">
-        <v>2000</v>
-      </c>
-      <c r="G274" t="s">
-        <v>36</v>
-      </c>
-      <c r="H274" t="s">
-        <v>62</v>
-      </c>
-      <c r="I274" t="s">
-        <v>23</v>
-      </c>
-      <c r="J274" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A275">
-        <v>100271</v>
-      </c>
-      <c r="B275" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C275" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D275" s="5">
-        <v>20090021</v>
-      </c>
-      <c r="E275" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F275">
-        <v>9000</v>
-      </c>
-      <c r="G275" t="s">
-        <v>21</v>
-      </c>
-      <c r="H275" t="s">
-        <v>66</v>
-      </c>
-      <c r="I275" t="s">
-        <v>23</v>
-      </c>
-      <c r="J275" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A276">
-        <v>100272</v>
-      </c>
-      <c r="B276" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C276" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D276" s="5">
-        <v>20090022</v>
-      </c>
-      <c r="E276" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F276">
-        <v>9000</v>
-      </c>
-      <c r="G276" t="s">
-        <v>21</v>
-      </c>
-      <c r="H276" t="s">
-        <v>66</v>
-      </c>
-      <c r="I276" t="s">
-        <v>23</v>
-      </c>
-      <c r="J276" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A277">
-        <v>100273</v>
-      </c>
-      <c r="B277" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C277" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D277" s="5">
-        <v>20090023</v>
-      </c>
-      <c r="E277" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F277">
-        <v>9000</v>
-      </c>
-      <c r="G277" t="s">
-        <v>21</v>
-      </c>
-      <c r="H277" t="s">
-        <v>66</v>
-      </c>
-      <c r="I277" t="s">
-        <v>23</v>
-      </c>
-      <c r="J277" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A278">
-        <v>100274</v>
-      </c>
-      <c r="B278" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D278" s="5">
-        <v>20090021</v>
-      </c>
-      <c r="E278" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F278">
-        <v>7000</v>
-      </c>
-      <c r="G278" t="s">
-        <v>28</v>
-      </c>
-      <c r="H278" t="s">
-        <v>66</v>
-      </c>
-      <c r="I278" t="s">
-        <v>23</v>
-      </c>
-      <c r="J278" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A279">
-        <v>100275</v>
-      </c>
-      <c r="B279" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C279" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D279" s="5">
-        <v>20090022</v>
-      </c>
-      <c r="E279" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F279">
-        <v>7000</v>
-      </c>
-      <c r="G279" t="s">
-        <v>28</v>
-      </c>
-      <c r="H279" t="s">
-        <v>66</v>
-      </c>
-      <c r="I279" t="s">
-        <v>23</v>
-      </c>
-      <c r="J279" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A280">
-        <v>100276</v>
-      </c>
-      <c r="B280" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D280" s="5">
-        <v>20090023</v>
-      </c>
-      <c r="E280" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F280">
-        <v>7000</v>
-      </c>
-      <c r="G280" t="s">
-        <v>28</v>
-      </c>
-      <c r="H280" t="s">
-        <v>66</v>
-      </c>
-      <c r="I280" t="s">
-        <v>23</v>
-      </c>
-      <c r="J280" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A281">
-        <v>100277</v>
-      </c>
-      <c r="B281" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C281" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D281" s="5">
-        <v>20090021</v>
-      </c>
-      <c r="E281" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F281">
-        <v>5000</v>
-      </c>
-      <c r="G281" t="s">
-        <v>31</v>
-      </c>
-      <c r="H281" t="s">
-        <v>66</v>
-      </c>
-      <c r="I281" t="s">
-        <v>23</v>
-      </c>
-      <c r="J281" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A282">
-        <v>100278</v>
-      </c>
-      <c r="B282" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D282" s="5">
-        <v>20090022</v>
-      </c>
-      <c r="E282" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F282">
-        <v>5000</v>
-      </c>
-      <c r="G282" t="s">
-        <v>31</v>
-      </c>
-      <c r="H282" t="s">
-        <v>66</v>
-      </c>
-      <c r="I282" t="s">
-        <v>23</v>
-      </c>
-      <c r="J282" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A283">
-        <v>100279</v>
-      </c>
-      <c r="B283" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D283" s="5">
-        <v>20090023</v>
-      </c>
-      <c r="E283" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F283">
-        <v>5000</v>
-      </c>
-      <c r="G283" t="s">
-        <v>31</v>
-      </c>
-      <c r="H283" t="s">
-        <v>66</v>
-      </c>
-      <c r="I283" t="s">
-        <v>23</v>
-      </c>
-      <c r="J283" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A284">
-        <v>100280</v>
-      </c>
-      <c r="B284" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D284" s="5">
-        <v>20090021</v>
-      </c>
-      <c r="E284" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F284">
-        <v>4000</v>
-      </c>
-      <c r="G284" t="s">
-        <v>34</v>
-      </c>
-      <c r="H284" t="s">
-        <v>66</v>
-      </c>
-      <c r="I284" t="s">
-        <v>23</v>
-      </c>
-      <c r="J284" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A285">
-        <v>100281</v>
-      </c>
-      <c r="B285" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C285" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D285" s="5">
-        <v>20090022</v>
-      </c>
-      <c r="E285" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F285">
-        <v>4000</v>
-      </c>
-      <c r="G285" t="s">
-        <v>34</v>
-      </c>
-      <c r="H285" t="s">
-        <v>66</v>
-      </c>
-      <c r="I285" t="s">
-        <v>23</v>
-      </c>
-      <c r="J285" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A286">
-        <v>100282</v>
-      </c>
-      <c r="B286" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C286" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D286" s="5">
-        <v>20090023</v>
-      </c>
-      <c r="E286" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F286">
-        <v>4000</v>
-      </c>
-      <c r="G286" t="s">
-        <v>34</v>
-      </c>
-      <c r="H286" t="s">
-        <v>66</v>
-      </c>
-      <c r="I286" t="s">
-        <v>23</v>
-      </c>
-      <c r="J286" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A287">
-        <v>100283</v>
-      </c>
-      <c r="B287" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D287" s="5">
-        <v>20090021</v>
-      </c>
-      <c r="E287" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F287">
-        <v>2000</v>
-      </c>
-      <c r="G287" t="s">
-        <v>36</v>
-      </c>
-      <c r="H287" t="s">
-        <v>66</v>
-      </c>
-      <c r="I287" t="s">
-        <v>23</v>
-      </c>
-      <c r="J287" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A288">
-        <v>100284</v>
-      </c>
-      <c r="B288" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C288" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D288" s="5">
-        <v>20090022</v>
-      </c>
-      <c r="E288" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F288">
-        <v>2000</v>
-      </c>
-      <c r="G288" t="s">
-        <v>36</v>
-      </c>
-      <c r="H288" t="s">
-        <v>66</v>
-      </c>
-      <c r="I288" t="s">
-        <v>23</v>
-      </c>
-      <c r="J288" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A289">
-        <v>100285</v>
-      </c>
-      <c r="B289" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D289" s="5">
-        <v>20090023</v>
-      </c>
-      <c r="E289" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F289">
-        <v>2000</v>
-      </c>
-      <c r="G289" t="s">
-        <v>36</v>
-      </c>
-      <c r="H289" t="s">
-        <v>66</v>
-      </c>
-      <c r="I289" t="s">
-        <v>23</v>
-      </c>
-      <c r="J289" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A290">
-        <v>100286</v>
-      </c>
-      <c r="B290" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C290" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D290" s="5">
-        <v>20120021</v>
-      </c>
-      <c r="E290" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F290">
-        <v>9000</v>
-      </c>
-      <c r="G290" t="s">
-        <v>21</v>
-      </c>
-      <c r="H290" t="s">
-        <v>70</v>
-      </c>
-      <c r="I290" t="s">
-        <v>23</v>
-      </c>
-      <c r="J290" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A291">
-        <v>100287</v>
-      </c>
-      <c r="B291" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C291" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D291" s="5">
-        <v>20120022</v>
-      </c>
-      <c r="E291" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F291">
-        <v>9000</v>
-      </c>
-      <c r="G291" t="s">
-        <v>21</v>
-      </c>
-      <c r="H291" t="s">
-        <v>70</v>
-      </c>
-      <c r="I291" t="s">
-        <v>23</v>
-      </c>
-      <c r="J291" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A292">
-        <v>100288</v>
-      </c>
-      <c r="B292" s="4">
-        <v>10099</v>
-      </c>
-      <c r="C292" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D292" s="5">
-        <v>20120023</v>
-      </c>
-      <c r="E292" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F292">
-        <v>9000</v>
-      </c>
-      <c r="G292" t="s">
-        <v>21</v>
-      </c>
-      <c r="H292" t="s">
-        <v>70</v>
-      </c>
-      <c r="I292" t="s">
-        <v>23</v>
-      </c>
-      <c r="J292" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A293">
-        <v>100289</v>
-      </c>
-      <c r="B293" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C293" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D293" s="5">
-        <v>20120021</v>
-      </c>
-      <c r="E293" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F293">
-        <v>7000</v>
-      </c>
-      <c r="G293" t="s">
-        <v>28</v>
-      </c>
-      <c r="H293" t="s">
-        <v>70</v>
-      </c>
-      <c r="I293" t="s">
-        <v>23</v>
-      </c>
-      <c r="J293" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A294">
-        <v>100290</v>
-      </c>
-      <c r="B294" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C294" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D294" s="5">
-        <v>20120022</v>
-      </c>
-      <c r="E294" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F294">
-        <v>7000</v>
-      </c>
-      <c r="G294" t="s">
-        <v>28</v>
-      </c>
-      <c r="H294" t="s">
-        <v>70</v>
-      </c>
-      <c r="I294" t="s">
-        <v>23</v>
-      </c>
-      <c r="J294" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A295">
-        <v>100291</v>
-      </c>
-      <c r="B295" s="4">
-        <v>10075</v>
-      </c>
-      <c r="C295" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D295" s="5">
-        <v>20120023</v>
-      </c>
-      <c r="E295" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F295">
-        <v>7000</v>
-      </c>
-      <c r="G295" t="s">
-        <v>28</v>
-      </c>
-      <c r="H295" t="s">
-        <v>70</v>
-      </c>
-      <c r="I295" t="s">
-        <v>23</v>
-      </c>
-      <c r="J295" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A296">
-        <v>100292</v>
-      </c>
-      <c r="B296" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C296" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D296" s="5">
-        <v>20120021</v>
-      </c>
-      <c r="E296" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F296">
-        <v>5000</v>
-      </c>
-      <c r="G296" t="s">
-        <v>31</v>
-      </c>
-      <c r="H296" t="s">
-        <v>70</v>
-      </c>
-      <c r="I296" t="s">
-        <v>23</v>
-      </c>
-      <c r="J296" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A297">
-        <v>100293</v>
-      </c>
-      <c r="B297" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C297" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D297" s="5">
-        <v>20120022</v>
-      </c>
-      <c r="E297" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F297">
-        <v>5000</v>
-      </c>
-      <c r="G297" t="s">
-        <v>31</v>
-      </c>
-      <c r="H297" t="s">
-        <v>70</v>
-      </c>
-      <c r="I297" t="s">
-        <v>23</v>
-      </c>
-      <c r="J297" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A298">
-        <v>100294</v>
-      </c>
-      <c r="B298" s="4">
-        <v>10050</v>
-      </c>
-      <c r="C298" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D298" s="5">
-        <v>20120023</v>
-      </c>
-      <c r="E298" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F298">
-        <v>5000</v>
-      </c>
-      <c r="G298" t="s">
-        <v>31</v>
-      </c>
-      <c r="H298" t="s">
-        <v>70</v>
-      </c>
-      <c r="I298" t="s">
-        <v>23</v>
-      </c>
-      <c r="J298" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A299">
-        <v>100295</v>
-      </c>
-      <c r="B299" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C299" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D299" s="5">
-        <v>20120021</v>
-      </c>
-      <c r="E299" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F299">
-        <v>4000</v>
-      </c>
-      <c r="G299" t="s">
-        <v>34</v>
-      </c>
-      <c r="H299" t="s">
-        <v>70</v>
-      </c>
-      <c r="I299" t="s">
-        <v>23</v>
-      </c>
-      <c r="J299" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A300">
-        <v>100296</v>
-      </c>
-      <c r="B300" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C300" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D300" s="5">
-        <v>20120022</v>
-      </c>
-      <c r="E300" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F300">
-        <v>4000</v>
-      </c>
-      <c r="G300" t="s">
-        <v>34</v>
-      </c>
-      <c r="H300" t="s">
-        <v>70</v>
-      </c>
-      <c r="I300" t="s">
-        <v>23</v>
-      </c>
-      <c r="J300" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A301">
-        <v>100297</v>
-      </c>
-      <c r="B301" s="4">
-        <v>10025</v>
-      </c>
-      <c r="C301" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D301" s="5">
-        <v>20120023</v>
-      </c>
-      <c r="E301" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F301">
-        <v>4000</v>
-      </c>
-      <c r="G301" t="s">
-        <v>34</v>
-      </c>
-      <c r="H301" t="s">
-        <v>70</v>
-      </c>
-      <c r="I301" t="s">
-        <v>23</v>
-      </c>
-      <c r="J301" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A302">
-        <v>100298</v>
-      </c>
-      <c r="B302" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C302" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D302" s="5">
-        <v>20120021</v>
-      </c>
-      <c r="E302" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F302">
-        <v>2000</v>
-      </c>
-      <c r="G302" t="s">
-        <v>36</v>
-      </c>
-      <c r="H302" t="s">
-        <v>70</v>
-      </c>
-      <c r="I302" t="s">
-        <v>23</v>
-      </c>
-      <c r="J302" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A303">
-        <v>100299</v>
-      </c>
-      <c r="B303" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C303" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D303" s="5">
-        <v>20120022</v>
-      </c>
-      <c r="E303" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F303">
-        <v>2000</v>
-      </c>
-      <c r="G303" t="s">
-        <v>36</v>
-      </c>
-      <c r="H303" t="s">
-        <v>70</v>
-      </c>
-      <c r="I303" t="s">
-        <v>23</v>
-      </c>
-      <c r="J303" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A304">
-        <v>100300</v>
-      </c>
-      <c r="B304" s="4">
-        <v>10001</v>
-      </c>
-      <c r="C304" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D304" s="5">
-        <v>20120023</v>
-      </c>
-      <c r="E304" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F304">
-        <v>2000</v>
-      </c>
-      <c r="G304" t="s">
-        <v>36</v>
-      </c>
-      <c r="H304" t="s">
-        <v>70</v>
-      </c>
-      <c r="I304" t="s">
-        <v>23</v>
-      </c>
-      <c r="J304" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>